--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\星杯传说工程\星杯传说2\星杯传说\Table\Design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\星杯传说工程\星杯传说2\xianyu_xingbei\Table\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7424C9-C4A9-4009-B374-5CFE01DC16F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657AC6C0-5F44-4C26-9E0E-D075962F743B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="690" yWindow="510" windowWidth="22350" windowHeight="13170" tabRatio="615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="23" r:id="rId1"/>
+    <sheet name="技能.csv" sheetId="23" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="标准击退速度">#REF!</definedName>
@@ -71,6 +71,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -398,9 +415,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CC7036-BBDA-4BEE-B966-A7D917172811}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E30F08-593B-48A3-9299-2637B691DA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="1547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3903" uniqueCount="1555">
   <si>
     <t>类型</t>
   </si>
@@ -5873,6 +5873,30 @@
   <si>
     <t>【星石】（【攻击行动】结束时发动）你摸１张牌[强制]、＋１【剑气】，额外＋１【攻击行动】。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态底色</t>
+  </si>
+  <si>
+    <t>status_color</t>
+  </si>
+  <si>
+    <t>#44D647</t>
+  </si>
+  <si>
+    <t>#0060FF</t>
+  </si>
+  <si>
+    <t>#672E77</t>
+  </si>
+  <si>
+    <t>#FA2727</t>
+  </si>
+  <si>
+    <t>#FF531E</t>
+  </si>
+  <si>
+    <t>#9E9E9E</t>
   </si>
 </sst>
 </file>
@@ -6226,7 +6250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5839A4A7-E3EE-408B-ABC6-26D91AFB7BC6}">
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.06640625" bestFit="1" customWidth="1"/>
@@ -6248,7 +6272,7 @@
     <col min="18" max="18" width="129.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>109</v>
       </c>
@@ -6303,8 +6327,11 @@
       <c r="R1" s="3" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S1" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -6359,8 +6386,11 @@
       <c r="R2" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S2" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -6415,8 +6445,11 @@
       <c r="R3" t="s">
         <v>1232</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1192</v>
       </c>
@@ -6454,7 +6487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>1193</v>
       </c>
@@ -6501,7 +6534,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>1194</v>
       </c>
@@ -6548,7 +6581,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>1195</v>
       </c>
@@ -6595,7 +6628,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>1196</v>
       </c>
@@ -6642,7 +6675,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>1197</v>
       </c>
@@ -6694,8 +6727,11 @@
       <c r="R9" t="s">
         <v>1236</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S9" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>1198</v>
       </c>
@@ -6747,8 +6783,11 @@
       <c r="R10" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S10" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>1199</v>
       </c>
@@ -6795,7 +6834,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>1200</v>
       </c>
@@ -6842,7 +6881,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>1201</v>
       </c>
@@ -6894,8 +6933,11 @@
       <c r="R13" t="s">
         <v>1540</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S13" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>1202</v>
       </c>
@@ -6942,7 +6984,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>1203</v>
       </c>
@@ -6992,7 +7034,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>1204</v>
       </c>
@@ -7039,7 +7081,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>1205</v>
       </c>
@@ -7086,7 +7128,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>1206</v>
       </c>
@@ -7141,8 +7183,11 @@
       <c r="R18" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S18" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>1207</v>
       </c>
@@ -7189,7 +7234,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>1208</v>
       </c>
@@ -7244,8 +7289,11 @@
       <c r="R20" t="s">
         <v>1244</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S20" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>1209</v>
       </c>
@@ -7292,7 +7340,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>1210</v>
       </c>
@@ -7342,7 +7390,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>1211</v>
       </c>
@@ -7392,7 +7440,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>1212</v>
       </c>
@@ -7447,8 +7495,11 @@
       <c r="R24" t="s">
         <v>1545</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S24" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>1213</v>
       </c>
@@ -7503,8 +7554,11 @@
       <c r="R25" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S25" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>1214</v>
       </c>
@@ -7554,7 +7608,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>1215</v>
       </c>
@@ -7606,8 +7660,11 @@
       <c r="R27" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S27" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>1216</v>
       </c>
@@ -7662,8 +7719,11 @@
       <c r="R28" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S28" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>1217</v>
       </c>
@@ -7715,8 +7775,11 @@
       <c r="R29" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S29" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>1218</v>
       </c>
@@ -7766,7 +7829,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>1219</v>
       </c>
@@ -7821,8 +7884,11 @@
       <c r="R31" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S31" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>1220</v>
       </c>
@@ -7877,8 +7943,11 @@
       <c r="R32" t="s">
         <v>1541</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S32" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>1221</v>
       </c>
@@ -7930,8 +7999,11 @@
       <c r="R33" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S33" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>1222</v>
       </c>
@@ -7986,8 +8058,11 @@
       <c r="R34" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S34" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>1223</v>
       </c>
@@ -8042,8 +8117,11 @@
       <c r="R35" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S35" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>1224</v>
       </c>
@@ -8098,8 +8176,11 @@
       <c r="R36" t="s">
         <v>1258</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S36" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>1225</v>
       </c>
@@ -8154,8 +8235,11 @@
       <c r="R37" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S37" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>1226</v>
       </c>
@@ -8210,8 +8294,11 @@
       <c r="R38" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S38" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>1227</v>
       </c>
@@ -8266,8 +8353,11 @@
       <c r="R39" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S39" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>1228</v>
       </c>
@@ -8322,8 +8412,11 @@
       <c r="R40" t="s">
         <v>1262</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S40" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>1229</v>
       </c>
@@ -8375,8 +8468,11 @@
       <c r="R41" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S41" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>1230</v>
       </c>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\星杯传说工程\星杯传说2\xianyu_xingbei\Table\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B63DDA-4275-4BCE-B511-1EF31A30DF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBC0EB4-1CF2-4680-9DEA-5D659D903CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8573" yWindow="285" windowWidth="14415" windowHeight="13170" tabRatio="631" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3872" uniqueCount="1585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3876" uniqueCount="1584">
   <si>
     <t>类型</t>
   </si>
@@ -4643,9 +4643,6 @@
     <t>技能#剑魂守护;技能#佯攻;技能#剑气斩;技能#天使与恶魔;技能#天使之魂;技能#恶魔之魂;技能#不屈意志</t>
   </si>
   <si>
-    <t>技能#挑衅;技能#禁断之力;技能#怒吼;技能#明镜止水;技能#死斗;技能#精疲力竭;技能#勇者之心</t>
-  </si>
-  <si>
     <t>技能#生命之火;技能#舞动;技能#毒粉;技能#朝圣;技能#镜花水月;技能#凋零;技能#蛹化;技能#倒逆之蝶</t>
   </si>
   <si>
@@ -5346,10 +5343,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>（对自己造成２点法术伤害③）你选择以下一项发动：●转移【同生共死】的目标。●移除【同生共死】。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（仅【流血形态】下发动）你弃２张牌，你＋１[治疗]。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5358,10 +5351,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>（摸２张牌【强制】，将【同生共死】放置于目标角色面前）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>【宝石】对目标角色造成２点法术伤害③，你弃３张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5905,10 +5894,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>技能#血之悲鸣;技能#同生共死;技能#血之哀伤;技能#逆流;技能#流血;技能#血之诅咒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>选1名目标摸牌，你弃3张牌，选好后点「确定」</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5971,13 +5956,25 @@
   </si>
   <si>
     <t>指定一名角色弃 1 张牌</t>
+  </si>
+  <si>
+    <t>技能#血之悲鸣;技能#逆流;技能#流血;技能#血之哀伤;技能#同生共死;技能#血之诅咒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（摸２张牌【强制】，将【同生共死】放置于目标角色面前）#●在【普通形态】下，你和他手牌上限各-2。#●在【流血形态】下，你和他手牌上限各+1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能#勇者之心;技能#怒吼;技能#精疲力竭;技能#明镜止水;技能#挑衅;技能#禁断之力;技能#死斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6037,6 +6034,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6058,7 +6063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -6073,6 +6078,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6386,7 +6393,7 @@
         <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1152</v>
@@ -6416,10 +6423,10 @@
         <v>446</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>270</v>
@@ -6445,7 +6452,7 @@
         <v>109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C2" t="s">
         <v>1153</v>
@@ -6475,10 +6482,10 @@
         <v>447</v>
       </c>
       <c r="L2" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>271</v>
@@ -6504,7 +6511,7 @@
         <v>110</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -6537,7 +6544,7 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>110</v>
@@ -6563,7 +6570,7 @@
         <v>1154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6601,7 +6608,7 @@
         <v>1155</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6640,7 +6647,7 @@
         <v>375</v>
       </c>
       <c r="S5" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
@@ -6648,7 +6655,7 @@
         <v>1156</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -6687,7 +6694,7 @@
         <v>376</v>
       </c>
       <c r="S6" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.4">
@@ -6695,7 +6702,7 @@
         <v>1157</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -6742,7 +6749,7 @@
         <v>1158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -6789,7 +6796,7 @@
         <v>1159</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -6819,10 +6826,10 @@
         <v>448</v>
       </c>
       <c r="L9" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="M9" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>284</v>
@@ -6845,7 +6852,7 @@
         <v>1160</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -6875,10 +6882,10 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="M10" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>286</v>
@@ -6901,7 +6908,7 @@
         <v>1161</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -6948,7 +6955,7 @@
         <v>1162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -6987,7 +6994,7 @@
         <v>382</v>
       </c>
       <c r="S12" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
@@ -6995,7 +7002,7 @@
         <v>1163</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -7025,10 +7032,10 @@
         <v>450</v>
       </c>
       <c r="L13" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="M13" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>291</v>
@@ -7043,7 +7050,7 @@
         <v>383</v>
       </c>
       <c r="S13" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
@@ -7051,7 +7058,7 @@
         <v>1164</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -7098,7 +7105,7 @@
         <v>1165</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -7148,7 +7155,7 @@
         <v>1166</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -7195,7 +7202,7 @@
         <v>1167</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -7242,7 +7249,7 @@
         <v>1168</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -7272,10 +7279,10 @@
         <v>451</v>
       </c>
       <c r="L18" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M18" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>299</v>
@@ -7301,7 +7308,7 @@
         <v>1169</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -7340,7 +7347,7 @@
         <v>391</v>
       </c>
       <c r="S19" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.4">
@@ -7348,7 +7355,7 @@
         <v>1170</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -7378,10 +7385,10 @@
         <v>452</v>
       </c>
       <c r="L20" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="M20" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>302</v>
@@ -7407,7 +7414,7 @@
         <v>1171</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C21">
         <v>17</v>
@@ -7454,7 +7461,7 @@
         <v>1172</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -7504,7 +7511,7 @@
         <v>1173</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C23">
         <v>19</v>
@@ -7554,7 +7561,7 @@
         <v>1174</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -7584,10 +7591,10 @@
         <v>453</v>
       </c>
       <c r="L24" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="M24" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>308</v>
@@ -7605,7 +7612,7 @@
         <v>400</v>
       </c>
       <c r="S24" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
@@ -7613,7 +7620,7 @@
         <v>1175</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C25">
         <v>21</v>
@@ -7643,10 +7650,10 @@
         <v>454</v>
       </c>
       <c r="L25" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M25" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>311</v>
@@ -7664,7 +7671,7 @@
         <v>402</v>
       </c>
       <c r="S25" t="s">
-        <v>1209</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
@@ -7672,7 +7679,7 @@
         <v>1176</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C26">
         <v>22</v>
@@ -7714,7 +7721,7 @@
         <v>404</v>
       </c>
       <c r="S26" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
@@ -7722,7 +7729,7 @@
         <v>1177</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C27">
         <v>23</v>
@@ -7752,10 +7759,10 @@
         <v>455</v>
       </c>
       <c r="L27" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M27" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>314</v>
@@ -7770,7 +7777,7 @@
         <v>405</v>
       </c>
       <c r="S27" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
@@ -7778,7 +7785,7 @@
         <v>1178</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C28">
         <v>24</v>
@@ -7808,10 +7815,10 @@
         <v>456</v>
       </c>
       <c r="L28" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="M28" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>318</v>
@@ -7829,7 +7836,7 @@
         <v>407</v>
       </c>
       <c r="S28" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.4">
@@ -7837,7 +7844,7 @@
         <v>1179</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -7867,10 +7874,10 @@
         <v>457</v>
       </c>
       <c r="L29" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="M29" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>320</v>
@@ -7885,7 +7892,7 @@
         <v>408</v>
       </c>
       <c r="S29" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.4">
@@ -7893,7 +7900,7 @@
         <v>1180</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -7935,7 +7942,7 @@
         <v>410</v>
       </c>
       <c r="S30" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.4">
@@ -7943,7 +7950,7 @@
         <v>1181</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C31">
         <v>27</v>
@@ -7973,10 +7980,10 @@
         <v>458</v>
       </c>
       <c r="L31" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="M31" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>324</v>
@@ -7994,7 +8001,7 @@
         <v>412</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.4">
@@ -8002,7 +8009,7 @@
         <v>1182</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C32">
         <v>28</v>
@@ -8032,10 +8039,10 @@
         <v>459</v>
       </c>
       <c r="L32" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M32" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>326</v>
@@ -8053,7 +8060,7 @@
         <v>414</v>
       </c>
       <c r="S32" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.4">
@@ -8061,7 +8068,7 @@
         <v>1183</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C33">
         <v>29</v>
@@ -8091,10 +8098,10 @@
         <v>460</v>
       </c>
       <c r="L33" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="M33" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>329</v>
@@ -8109,7 +8116,7 @@
         <v>415</v>
       </c>
       <c r="S33" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.4">
@@ -8117,7 +8124,7 @@
         <v>1184</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C34">
         <v>30</v>
@@ -8147,10 +8154,10 @@
         <v>461</v>
       </c>
       <c r="L34" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M34" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>332</v>
@@ -8168,7 +8175,7 @@
         <v>417</v>
       </c>
       <c r="S34" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.4">
@@ -8176,7 +8183,7 @@
         <v>1185</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -8206,10 +8213,10 @@
         <v>434</v>
       </c>
       <c r="L35" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="M35" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>334</v>
@@ -8227,7 +8234,7 @@
         <v>419</v>
       </c>
       <c r="S35" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.4">
@@ -8235,7 +8242,7 @@
         <v>1186</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -8265,10 +8272,10 @@
         <v>462</v>
       </c>
       <c r="L36" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="M36" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>337</v>
@@ -8286,7 +8293,7 @@
         <v>421</v>
       </c>
       <c r="S36" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.4">
@@ -8294,7 +8301,7 @@
         <v>1187</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C37">
         <v>33</v>
@@ -8324,10 +8331,10 @@
         <v>434</v>
       </c>
       <c r="L37" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="M37" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>435</v>
@@ -8345,7 +8352,7 @@
         <v>437</v>
       </c>
       <c r="S37" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.4">
@@ -8353,7 +8360,7 @@
         <v>1188</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C38">
         <v>34</v>
@@ -8383,10 +8390,10 @@
         <v>463</v>
       </c>
       <c r="L38" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="M38" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>339</v>
@@ -8404,7 +8411,7 @@
         <v>423</v>
       </c>
       <c r="S38" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.4">
@@ -8412,7 +8419,7 @@
         <v>1189</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C39">
         <v>35</v>
@@ -8442,10 +8449,10 @@
         <v>430</v>
       </c>
       <c r="L39" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="M39" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>341</v>
@@ -8463,7 +8470,7 @@
         <v>425</v>
       </c>
       <c r="S39" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.4">
@@ -8471,7 +8478,7 @@
         <v>1190</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C40">
         <v>36</v>
@@ -8501,10 +8508,10 @@
         <v>448</v>
       </c>
       <c r="L40" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="M40" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>343</v>
@@ -8522,7 +8529,7 @@
         <v>427</v>
       </c>
       <c r="S40" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.4">
@@ -8530,7 +8537,7 @@
         <v>1191</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C41">
         <v>37</v>
@@ -8560,7 +8567,7 @@
         <v>430</v>
       </c>
       <c r="L41" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>431</v>
@@ -8578,7 +8585,7 @@
         <v>433</v>
       </c>
       <c r="S41" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.4">
@@ -8586,7 +8593,7 @@
         <v>1192</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C42">
         <v>108</v>
@@ -8653,7 +8660,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -14211,25 +14218,25 @@
         <v>358</v>
       </c>
       <c r="G1" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="H1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="I1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="J1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K1" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="L1" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="M1" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="N1" t="s">
         <v>438</v>
@@ -14261,22 +14268,22 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="I2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="J2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K2" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="L2" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="M2" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="N2" t="s">
         <v>439</v>
@@ -14308,22 +14315,22 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="I3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="K3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="L3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="M3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="N3" t="s">
         <v>15</v>
@@ -14334,7 +14341,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B4">
         <v>103</v>
@@ -14378,7 +14385,7 @@
         <v>749</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>753</v>
@@ -14404,7 +14411,7 @@
         <v>749</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>756</v>
@@ -14430,7 +14437,7 @@
         <v>749</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>758</v>
@@ -14444,7 +14451,7 @@
         <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="D8" t="s">
         <v>747</v>
@@ -14456,7 +14463,7 @@
         <v>760</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>761</v>
@@ -14482,7 +14489,7 @@
         <v>749</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>763</v>
@@ -14508,7 +14515,7 @@
         <v>749</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>499</v>
@@ -14534,10 +14541,10 @@
         <v>749</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -14560,7 +14567,7 @@
         <v>767</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>768</v>
@@ -14586,7 +14593,7 @@
         <v>749</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>770</v>
@@ -14612,10 +14619,10 @@
         <v>749</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H14" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>772</v>
@@ -14641,7 +14648,7 @@
         <v>749</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>775</v>
@@ -14667,7 +14674,7 @@
         <v>749</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>777</v>
@@ -14693,7 +14700,7 @@
         <v>760</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>779</v>
@@ -14719,7 +14726,7 @@
         <v>749</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>781</v>
@@ -14745,7 +14752,7 @@
         <v>749</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>783</v>
@@ -14771,7 +14778,7 @@
         <v>749</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>785</v>
@@ -14797,7 +14804,7 @@
         <v>749</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>787</v>
@@ -14823,7 +14830,7 @@
         <v>749</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>789</v>
@@ -14849,7 +14856,7 @@
         <v>749</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>791</v>
@@ -14875,7 +14882,7 @@
         <v>760</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>465</v>
@@ -14904,7 +14911,7 @@
         <v>760</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>466</v>
@@ -14933,7 +14940,7 @@
         <v>749</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>798</v>
@@ -14959,10 +14966,10 @@
         <v>749</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H27" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>800</v>
@@ -14988,7 +14995,7 @@
         <v>767</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>803</v>
@@ -15014,13 +15021,13 @@
         <v>749</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H29" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="I29" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1" t="s">
@@ -15047,10 +15054,10 @@
         <v>749</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H30" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>467</v>
@@ -15079,10 +15086,10 @@
         <v>749</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H31" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="N31" t="s">
         <v>809</v>
@@ -15111,7 +15118,7 @@
         <v>767</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>812</v>
@@ -15137,10 +15144,10 @@
         <v>760</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H33" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>468</v>
@@ -15169,7 +15176,7 @@
         <v>749</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>470</v>
@@ -15198,10 +15205,10 @@
         <v>749</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H35" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>469</v>
@@ -15230,10 +15237,10 @@
         <v>749</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H36" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1" t="s">
@@ -15289,10 +15296,10 @@
         <v>760</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H38" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>825</v>
@@ -15318,13 +15325,13 @@
         <v>760</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H39" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="J39" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>827</v>
@@ -15350,10 +15357,10 @@
         <v>749</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H40" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>471</v>
@@ -15437,7 +15444,7 @@
         <v>767</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>473</v>
@@ -15466,7 +15473,7 @@
         <v>749</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>836</v>
@@ -15492,7 +15499,7 @@
         <v>749</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>838</v>
@@ -15518,7 +15525,7 @@
         <v>749</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>840</v>
@@ -15570,7 +15577,7 @@
         <v>749</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>474</v>
@@ -15581,7 +15588,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="B49">
         <v>906</v>
@@ -15599,7 +15606,7 @@
         <v>767</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>845</v>
@@ -15625,7 +15632,7 @@
         <v>749</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1" t="s">
@@ -15652,10 +15659,10 @@
         <v>749</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H51" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>475</v>
@@ -15684,10 +15691,10 @@
         <v>749</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H52" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>476</v>
@@ -15716,7 +15723,7 @@
         <v>749</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>853</v>
@@ -15742,10 +15749,10 @@
         <v>749</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H54" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>855</v>
@@ -15771,13 +15778,13 @@
         <v>749</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H55" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="I55" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>857</v>
@@ -15803,10 +15810,10 @@
         <v>767</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H56" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="N56" t="s">
         <v>859</v>
@@ -15835,7 +15842,7 @@
         <v>749</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>862</v>
@@ -15861,7 +15868,7 @@
         <v>749</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="N58" t="s">
         <v>864</v>
@@ -15890,7 +15897,7 @@
         <v>749</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>867</v>
@@ -15916,7 +15923,7 @@
         <v>749</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>869</v>
@@ -15942,7 +15949,7 @@
         <v>749</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>871</v>
@@ -15968,7 +15975,7 @@
         <v>749</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1" t="s">
@@ -15995,7 +16002,7 @@
         <v>749</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1" t="s">
@@ -16022,7 +16029,7 @@
         <v>767</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="N64" t="s">
         <v>877</v>
@@ -16051,7 +16058,7 @@
         <v>749</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>477</v>
@@ -16080,7 +16087,7 @@
         <v>749</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>883</v>
@@ -16106,7 +16113,7 @@
         <v>749</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1" t="s">
@@ -16133,7 +16140,7 @@
         <v>749</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1" t="s">
@@ -16160,7 +16167,7 @@
         <v>760</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="N69" t="s">
         <v>888</v>
@@ -16189,7 +16196,7 @@
         <v>760</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="N70" t="s">
         <v>891</v>
@@ -16216,7 +16223,7 @@
         <v>749</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1" t="s">
@@ -16243,7 +16250,7 @@
         <v>749</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1" t="s">
@@ -16270,7 +16277,7 @@
         <v>749</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>478</v>
@@ -16299,10 +16306,10 @@
         <v>749</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H74" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>899</v>
@@ -16331,7 +16338,7 @@
         <v>767</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>901</v>
@@ -16360,7 +16367,7 @@
         <v>749</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1" t="s">
@@ -16387,7 +16394,7 @@
         <v>749</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1" t="s">
@@ -16414,7 +16421,7 @@
         <v>749</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>479</v>
@@ -16443,7 +16450,7 @@
         <v>749</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1" t="s">
@@ -16470,7 +16477,7 @@
         <v>767</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1" t="s">
@@ -16497,13 +16504,13 @@
         <v>749</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H81" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="I81" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>746</v>
@@ -16532,7 +16539,7 @@
         <v>749</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="O82" s="1" t="s">
         <v>915</v>
@@ -16558,7 +16565,7 @@
         <v>749</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="N83" t="s">
         <v>917</v>
@@ -16587,10 +16594,10 @@
         <v>749</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H84" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>480</v>
@@ -16619,7 +16626,7 @@
         <v>749</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>490</v>
@@ -16645,13 +16652,13 @@
         <v>760</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H86" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="I86" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1" t="s">
@@ -16678,10 +16685,10 @@
         <v>749</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H87" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>925</v>
@@ -16710,7 +16717,7 @@
         <v>749</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>481</v>
@@ -16739,7 +16746,7 @@
         <v>749</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>482</v>
@@ -16768,10 +16775,10 @@
         <v>749</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H90" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="N90" t="s">
         <v>930</v>
@@ -16800,7 +16807,7 @@
         <v>749</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="N91" t="s">
         <v>933</v>
@@ -16829,7 +16836,7 @@
         <v>767</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1" t="s">
@@ -16856,7 +16863,7 @@
         <v>760</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1" t="s">
@@ -16883,7 +16890,7 @@
         <v>749</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>939</v>
@@ -16909,10 +16916,10 @@
         <v>749</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H95" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1" t="s">
@@ -16939,7 +16946,7 @@
         <v>767</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>483</v>
@@ -16968,7 +16975,7 @@
         <v>767</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="N97" t="s">
         <v>945</v>
@@ -17058,7 +17065,7 @@
         <v>950</v>
       </c>
       <c r="H100" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O100" s="1" t="s">
         <v>950</v>
@@ -17087,13 +17094,13 @@
         <v>952</v>
       </c>
       <c r="H101" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="I101" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="J101" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>952</v>
@@ -17171,7 +17178,7 @@
         <v>749</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="O104" s="1" t="s">
         <v>957</v>
@@ -17197,13 +17204,13 @@
         <v>749</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H105" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="I105" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="O105" s="1" t="s">
         <v>959</v>
@@ -17229,10 +17236,10 @@
         <v>749</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H106" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="O106" s="1" t="s">
         <v>961</v>
@@ -17258,10 +17265,10 @@
         <v>749</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H107" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="O107" s="1" t="s">
         <v>963</v>
@@ -17287,7 +17294,7 @@
         <v>760</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="O108" s="1" t="s">
         <v>965</v>
@@ -17329,7 +17336,7 @@
         <v>749</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="O110" s="1" t="s">
         <v>967</v>
@@ -17355,7 +17362,7 @@
         <v>749</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="O111" s="1" t="s">
         <v>969</v>
@@ -17381,10 +17388,10 @@
         <v>749</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H112" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="O112" s="1" t="s">
         <v>971</v>
@@ -17413,7 +17420,7 @@
         <v>492</v>
       </c>
       <c r="H113" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="O113" s="1" t="s">
         <v>492</v>
@@ -17465,200 +17472,202 @@
         <v>760</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H115" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="1" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A116" s="1" t="s">
+    <row r="116" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="12">
         <v>2107</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="12" t="s">
         <v>976</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="G116" s="1"/>
-      <c r="O116" s="1" t="s">
+      <c r="G116" s="13" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A117" s="1" t="s">
+      <c r="O116" s="13" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="12">
         <v>2103</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G117" s="13" t="s">
+        <v>1391</v>
+      </c>
+      <c r="O117" s="13" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="B118" s="12">
+        <v>2106</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="G118" s="13" t="s">
         <v>1392</v>
       </c>
-      <c r="O117" s="1" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A118" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="B118">
-        <v>2106</v>
-      </c>
-      <c r="C118" t="s">
-        <v>979</v>
-      </c>
-      <c r="D118" t="s">
-        <v>752</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="O118" s="13" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="B119" s="12">
+        <v>2104</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="E119" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F119" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="G119" s="13" t="s">
         <v>1393</v>
       </c>
-      <c r="O118" s="1" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A119" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B119">
-        <v>2104</v>
-      </c>
-      <c r="C119" t="s">
-        <v>981</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="N119" s="13"/>
+      <c r="O119" s="13" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="B120" s="12">
+        <v>2101</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="G120" s="13" t="s">
+        <v>1394</v>
+      </c>
+      <c r="N120" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="O120" s="13" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="B121" s="12">
+        <v>2102</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="D121" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="E119" t="s">
-        <v>748</v>
-      </c>
-      <c r="F119" t="s">
-        <v>749</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>1394</v>
-      </c>
-      <c r="N119" s="1"/>
-      <c r="O119" s="1" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A120" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B120">
-        <v>2101</v>
-      </c>
-      <c r="C120" t="s">
-        <v>983</v>
-      </c>
-      <c r="D120" t="s">
-        <v>774</v>
-      </c>
-      <c r="E120" t="s">
-        <v>793</v>
-      </c>
-      <c r="F120" t="s">
-        <v>749</v>
-      </c>
-      <c r="G120" s="1" t="s">
+      <c r="E121" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="G121" s="13" t="s">
         <v>1395</v>
       </c>
-      <c r="N120" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="O120" s="1" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A121" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="B121">
-        <v>2102</v>
-      </c>
-      <c r="C121" t="s">
-        <v>985</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="H121" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="O121" s="13" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="13" t="s">
+        <v>637</v>
+      </c>
+      <c r="B122" s="12">
+        <v>2105</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="D122" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E122" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="F121" t="s">
-        <v>760</v>
-      </c>
-      <c r="G121" s="1" t="s">
+      <c r="F122" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="G122" s="13" t="s">
         <v>1396</v>
       </c>
-      <c r="H121" t="s">
-        <v>1257</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A122" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B122">
-        <v>2105</v>
-      </c>
-      <c r="C122" t="s">
-        <v>987</v>
-      </c>
-      <c r="D122" t="s">
-        <v>747</v>
-      </c>
-      <c r="E122" t="s">
-        <v>759</v>
-      </c>
-      <c r="F122" t="s">
-        <v>767</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>1397</v>
-      </c>
-      <c r="O122" s="1" t="s">
+      <c r="O122" s="13" t="s">
         <v>988</v>
       </c>
     </row>
@@ -17682,7 +17691,7 @@
         <v>749</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1" t="s">
@@ -17709,7 +17718,7 @@
         <v>749</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="N124" t="s">
         <v>992</v>
@@ -17738,16 +17747,16 @@
         <v>749</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H125" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="I125" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="J125" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1" t="s">
@@ -17774,10 +17783,10 @@
         <v>749</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="H126" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="N126" t="s">
         <v>997</v>
@@ -17806,7 +17815,7 @@
         <v>749</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="N127" t="s">
         <v>1000</v>
@@ -17835,7 +17844,7 @@
         <v>749</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="N128" s="1" t="s">
         <v>485</v>
@@ -17864,19 +17873,19 @@
         <v>749</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H129" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I129" t="s">
         <v>1259</v>
       </c>
-      <c r="I129" t="s">
-        <v>1260</v>
-      </c>
       <c r="J129" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="K129" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1" t="s">
@@ -17903,7 +17912,7 @@
         <v>767</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>1006</v>
@@ -17929,16 +17938,16 @@
         <v>749</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1405</v>
+        <v>1008</v>
       </c>
       <c r="H131" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="I131" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="J131" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>1008</v>
@@ -17964,7 +17973,7 @@
         <v>749</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>23</v>
+        <v>1010</v>
       </c>
       <c r="N132" s="1"/>
       <c r="O132" s="1" t="s">
@@ -17991,7 +18000,7 @@
         <v>749</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="N133" t="s">
         <v>1012</v>
@@ -18020,16 +18029,16 @@
         <v>749</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="H134" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="I134" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="J134" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="N134" t="s">
         <v>1014</v>
@@ -18058,7 +18067,7 @@
         <v>749</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1408</v>
+        <v>1582</v>
       </c>
       <c r="N135" s="1" t="s">
         <v>486</v>
@@ -18087,7 +18096,7 @@
         <v>767</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="N136" t="s">
         <v>1018</v>
@@ -18116,7 +18125,7 @@
         <v>749</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="O137" s="1" t="s">
         <v>1021</v>
@@ -18142,13 +18151,13 @@
         <v>749</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="H138" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="I138" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="N138" t="s">
         <v>1023</v>
@@ -18177,10 +18186,10 @@
         <v>749</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="H139" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="N139" s="1"/>
       <c r="O139" s="1" t="s">
@@ -18207,10 +18216,10 @@
         <v>749</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="H140" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="N140" s="1"/>
       <c r="O140" s="1" t="s">
@@ -18237,10 +18246,10 @@
         <v>749</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="H141" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="O141" s="1" t="s">
         <v>1030</v>
@@ -18266,10 +18275,10 @@
         <v>749</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="H142" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="N142" s="1"/>
       <c r="O142" s="1" t="s">
@@ -18296,7 +18305,7 @@
         <v>767</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="N143" t="s">
         <v>1034</v>
@@ -18325,16 +18334,16 @@
         <v>760</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="H144" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I144" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="J144" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="N144" t="s">
         <v>1037</v>
@@ -18363,7 +18372,7 @@
         <v>749</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>1039</v>
@@ -18389,7 +18398,7 @@
         <v>749</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="N146" t="s">
         <v>1041</v>
@@ -18418,7 +18427,7 @@
         <v>749</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1" t="s">
@@ -18445,25 +18454,25 @@
         <v>749</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="H148" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="I148" t="s">
+        <v>1551</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L148" t="s">
         <v>1554</v>
       </c>
-      <c r="J148" t="s">
+      <c r="M148" t="s">
         <v>1555</v>
-      </c>
-      <c r="K148" t="s">
-        <v>1556</v>
-      </c>
-      <c r="L148" t="s">
-        <v>1557</v>
-      </c>
-      <c r="M148" t="s">
-        <v>1558</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>504</v>
@@ -18489,10 +18498,10 @@
         <v>760</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="H149" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="O149" s="1" t="s">
         <v>1047</v>
@@ -18518,16 +18527,16 @@
         <v>749</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="H150" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="I150" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="J150" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>1049</v>
@@ -18553,10 +18562,10 @@
         <v>749</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H151" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="N151" t="s">
         <v>1051</v>
@@ -18585,10 +18594,10 @@
         <v>749</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="H152" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>497</v>
@@ -18614,19 +18623,19 @@
         <v>760</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="H153" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="I153" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="J153" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="K153" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>1054</v>
@@ -18655,16 +18664,16 @@
         <v>1056</v>
       </c>
       <c r="H154" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="I154" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="J154" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="K154" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="O154" s="1" t="s">
         <v>1056</v>
@@ -18698,13 +18707,13 @@
     </row>
     <row r="156" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="7" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="B156" s="8">
         <v>2704</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>747</v>
@@ -18716,13 +18725,13 @@
         <v>749</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="O156" s="7" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
@@ -18745,16 +18754,16 @@
         <v>749</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>1061</v>
@@ -18762,13 +18771,13 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="B158" s="10">
         <v>2701</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>747</v>
@@ -18780,19 +18789,19 @@
         <v>749</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
       <c r="H158" s="10" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="O158" s="9" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="159" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
@@ -18815,10 +18824,10 @@
         <v>767</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="O159" s="7" t="s">
         <v>1063</v>
@@ -18844,10 +18853,10 @@
         <v>760</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="O160" s="7" t="s">
         <v>1065</v>
@@ -18855,7 +18864,7 @@
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A161" s="1" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="B161">
         <v>2801</v>
@@ -18873,7 +18882,7 @@
         <v>749</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="O161" s="1" t="s">
         <v>1066</v>
@@ -18899,7 +18908,7 @@
         <v>749</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="N162" s="1"/>
       <c r="O162" s="1" t="s">
@@ -18926,13 +18935,13 @@
         <v>749</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="H163" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="I163" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>1069</v>
@@ -18958,7 +18967,7 @@
         <v>749</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>1071</v>
@@ -18984,7 +18993,7 @@
         <v>749</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>1073</v>
@@ -19010,7 +19019,7 @@
         <v>760</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="N166" s="1"/>
       <c r="O166" s="1" t="s">
@@ -19027,10 +19036,18 @@
       <c r="C167" t="s">
         <v>1076</v>
       </c>
+      <c r="D167" t="s">
+        <v>774</v>
+      </c>
+      <c r="E167" t="s">
+        <v>759</v>
+      </c>
       <c r="F167" t="s">
         <v>749</v>
       </c>
-      <c r="G167" s="1"/>
+      <c r="G167" s="1" t="s">
+        <v>1077</v>
+      </c>
       <c r="N167" t="s">
         <v>268</v>
       </c>
@@ -19058,7 +19075,7 @@
         <v>749</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="N168" s="1"/>
       <c r="O168" s="1" t="s">
@@ -19085,10 +19102,10 @@
         <v>749</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="H169" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="N169" s="1"/>
       <c r="O169" s="1" t="s">
@@ -19141,10 +19158,10 @@
         <v>749</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="H171" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="O171" s="1" t="s">
         <v>1086</v>
@@ -19170,10 +19187,10 @@
         <v>749</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="H172" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="N172" t="s">
         <v>1088</v>
@@ -19202,10 +19219,10 @@
         <v>760</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H173" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="N173" s="1"/>
       <c r="O173" s="1" t="s">
@@ -19261,7 +19278,7 @@
         <v>749</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="N175" t="s">
         <v>1096</v>
@@ -19290,16 +19307,16 @@
         <v>749</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="H176" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="I176" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="J176" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="N176" s="1"/>
       <c r="O176" s="1" t="s">
@@ -19329,7 +19346,7 @@
         <v>1101</v>
       </c>
       <c r="H177" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="O177" s="1" t="s">
         <v>1101</v>
@@ -19355,7 +19372,7 @@
         <v>749</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>498</v>
@@ -19381,7 +19398,7 @@
         <v>760</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="N179" t="s">
         <v>1104</v>
@@ -19410,10 +19427,10 @@
         <v>760</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="H180" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>1107</v>
@@ -19439,10 +19456,10 @@
         <v>749</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="H181" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>1109</v>
@@ -19469,13 +19486,13 @@
       </c>
       <c r="G182" s="1"/>
       <c r="H182" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I182" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="J182" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="N182" t="s">
         <v>269</v>
@@ -19523,19 +19540,19 @@
         <v>749</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="H184" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I184" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="J184" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="K184" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>507</v>
@@ -19561,22 +19578,22 @@
         <v>749</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="H185" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="I185" t="s">
+        <v>1547</v>
+      </c>
+      <c r="J185" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K185" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L185" t="s">
         <v>1550</v>
-      </c>
-      <c r="J185" t="s">
-        <v>1551</v>
-      </c>
-      <c r="K185" t="s">
-        <v>1552</v>
-      </c>
-      <c r="L185" t="s">
-        <v>1553</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>508</v>
@@ -19602,10 +19619,10 @@
         <v>767</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="H186" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="O186" s="1" t="s">
         <v>509</v>
@@ -19631,7 +19648,7 @@
         <v>749</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="O187" s="1"/>
     </row>
@@ -19656,7 +19673,7 @@
       </c>
       <c r="G188" s="1"/>
       <c r="H188" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O188" s="1"/>
     </row>
@@ -19683,10 +19700,10 @@
         <v>23</v>
       </c>
       <c r="H189" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="I189" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O189" s="1"/>
     </row>
@@ -19713,7 +19730,7 @@
         <v>23</v>
       </c>
       <c r="H190" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="O190" s="1"/>
     </row>
@@ -19738,7 +19755,7 @@
       </c>
       <c r="G191" s="1"/>
       <c r="H191" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="O191" s="1"/>
     </row>
@@ -19763,7 +19780,7 @@
       </c>
       <c r="G192" s="1"/>
       <c r="H192" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="O192" s="1"/>
     </row>
@@ -19832,7 +19849,7 @@
       </c>
       <c r="G195" s="1"/>
       <c r="H195" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="O195" s="1"/>
     </row>
@@ -19931,7 +19948,7 @@
         <v>23</v>
       </c>
       <c r="H199" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="O199" s="1"/>
     </row>
@@ -19956,7 +19973,7 @@
       </c>
       <c r="G200" s="1"/>
       <c r="H200" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="O200" s="1"/>
     </row>
@@ -20029,7 +20046,7 @@
         <v>23</v>
       </c>
       <c r="H203" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="O203" s="1"/>
     </row>
@@ -20054,7 +20071,7 @@
       </c>
       <c r="G204" s="1"/>
       <c r="H204" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="O204" s="1"/>
     </row>
@@ -20081,7 +20098,7 @@
         <v>23</v>
       </c>
       <c r="H205" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="O205" s="1"/>
     </row>
@@ -20108,7 +20125,7 @@
         <v>23</v>
       </c>
       <c r="H206" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="O206" s="1"/>
     </row>
@@ -20229,10 +20246,10 @@
         <v>23</v>
       </c>
       <c r="H211" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I211" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="O211" s="1"/>
     </row>
@@ -20259,7 +20276,7 @@
         <v>23</v>
       </c>
       <c r="H212" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="O212" s="1"/>
     </row>
@@ -20286,7 +20303,7 @@
         <v>23</v>
       </c>
       <c r="H213" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="O213" s="1"/>
     </row>
@@ -20311,7 +20328,7 @@
       </c>
       <c r="G214" s="1"/>
       <c r="H214" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="O214" s="1"/>
     </row>
@@ -20446,7 +20463,7 @@
       </c>
       <c r="G220" s="1"/>
       <c r="H220" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="O220" s="1"/>
     </row>
@@ -20471,7 +20488,7 @@
       </c>
       <c r="G221" s="1"/>
       <c r="H221" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="O221" s="1"/>
     </row>
@@ -20496,7 +20513,7 @@
       </c>
       <c r="G222" s="1"/>
       <c r="H222" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="O222" s="1"/>
     </row>
@@ -20619,7 +20636,7 @@
         <v>23</v>
       </c>
       <c r="H227" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O227" s="1"/>
     </row>
@@ -20665,10 +20682,10 @@
         <v>1146</v>
       </c>
       <c r="H229" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I229" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.4">
@@ -20691,7 +20708,7 @@
         <v>1146</v>
       </c>
       <c r="H230" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.4">

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\星杯传说工程\星杯传说2\xianyu_xingbei\Table\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBC0EB4-1CF2-4680-9DEA-5D659D903CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51222A25-88BB-4274-9F31-36DB6D531C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8573" yWindow="285" windowWidth="14415" windowHeight="13170" tabRatio="631" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>
@@ -5311,10 +5311,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>【宝石】（每当你承受法术伤害时发动⑥）你＋３点【怒气】。##＊【怒气】和【知性】为勇者专有指示物，上限各为４。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（我方每有１点士气下降）你＋１【黄色灵魂】。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5967,6 +5963,10 @@
   </si>
   <si>
     <t>技能#勇者之心;技能#怒吼;技能#精疲力竭;技能#明镜止水;技能#挑衅;技能#禁断之力;技能#死斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【宝石】（每当你承受法术伤害时发动⑥）你＋３点【怒气】。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6423,10 +6423,10 @@
         <v>446</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>270</v>
@@ -6482,10 +6482,10 @@
         <v>447</v>
       </c>
       <c r="L2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>271</v>
@@ -6544,7 +6544,7 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>110</v>
@@ -6647,7 +6647,7 @@
         <v>375</v>
       </c>
       <c r="S5" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
@@ -6694,7 +6694,7 @@
         <v>376</v>
       </c>
       <c r="S6" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.4">
@@ -6826,10 +6826,10 @@
         <v>448</v>
       </c>
       <c r="L9" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="M9" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>284</v>
@@ -6882,10 +6882,10 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="M10" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>286</v>
@@ -6994,7 +6994,7 @@
         <v>382</v>
       </c>
       <c r="S12" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
@@ -7032,10 +7032,10 @@
         <v>450</v>
       </c>
       <c r="L13" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="M13" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>291</v>
@@ -7050,7 +7050,7 @@
         <v>383</v>
       </c>
       <c r="S13" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
@@ -7279,10 +7279,10 @@
         <v>451</v>
       </c>
       <c r="L18" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M18" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>299</v>
@@ -7347,7 +7347,7 @@
         <v>391</v>
       </c>
       <c r="S19" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.4">
@@ -7385,10 +7385,10 @@
         <v>452</v>
       </c>
       <c r="L20" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="M20" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>302</v>
@@ -7591,10 +7591,10 @@
         <v>453</v>
       </c>
       <c r="L24" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="M24" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>308</v>
@@ -7612,7 +7612,7 @@
         <v>400</v>
       </c>
       <c r="S24" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
@@ -7650,10 +7650,10 @@
         <v>454</v>
       </c>
       <c r="L25" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M25" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>311</v>
@@ -7671,7 +7671,7 @@
         <v>402</v>
       </c>
       <c r="S25" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
@@ -7721,7 +7721,7 @@
         <v>404</v>
       </c>
       <c r="S26" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
@@ -7759,10 +7759,10 @@
         <v>455</v>
       </c>
       <c r="L27" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M27" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>314</v>
@@ -7777,7 +7777,7 @@
         <v>405</v>
       </c>
       <c r="S27" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
@@ -7815,10 +7815,10 @@
         <v>456</v>
       </c>
       <c r="L28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="M28" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>318</v>
@@ -7874,10 +7874,10 @@
         <v>457</v>
       </c>
       <c r="L29" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="M29" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>320</v>
@@ -7980,10 +7980,10 @@
         <v>458</v>
       </c>
       <c r="L31" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="M31" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>324</v>
@@ -8001,7 +8001,7 @@
         <v>412</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.4">
@@ -8039,10 +8039,10 @@
         <v>459</v>
       </c>
       <c r="L32" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M32" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>326</v>
@@ -8060,7 +8060,7 @@
         <v>414</v>
       </c>
       <c r="S32" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.4">
@@ -8098,10 +8098,10 @@
         <v>460</v>
       </c>
       <c r="L33" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="M33" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>329</v>
@@ -8116,7 +8116,7 @@
         <v>415</v>
       </c>
       <c r="S33" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.4">
@@ -8154,10 +8154,10 @@
         <v>461</v>
       </c>
       <c r="L34" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M34" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>332</v>
@@ -8213,10 +8213,10 @@
         <v>434</v>
       </c>
       <c r="L35" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="M35" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>334</v>
@@ -8272,10 +8272,10 @@
         <v>462</v>
       </c>
       <c r="L36" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="M36" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>337</v>
@@ -8331,10 +8331,10 @@
         <v>434</v>
       </c>
       <c r="L37" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="M37" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>435</v>
@@ -8390,10 +8390,10 @@
         <v>463</v>
       </c>
       <c r="L38" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="M38" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>339</v>
@@ -8449,10 +8449,10 @@
         <v>430</v>
       </c>
       <c r="L39" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="M39" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>341</v>
@@ -8508,10 +8508,10 @@
         <v>448</v>
       </c>
       <c r="L40" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="M40" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>343</v>
@@ -8567,7 +8567,7 @@
         <v>430</v>
       </c>
       <c r="L41" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>431</v>
@@ -14218,7 +14218,7 @@
         <v>358</v>
       </c>
       <c r="G1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H1" t="s">
         <v>1230</v>
@@ -14230,13 +14230,13 @@
         <v>1235</v>
       </c>
       <c r="K1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="L1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="M1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="N1" t="s">
         <v>438</v>
@@ -14277,13 +14277,13 @@
         <v>1236</v>
       </c>
       <c r="K2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="L2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="N2" t="s">
         <v>439</v>
@@ -14341,7 +14341,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B4">
         <v>103</v>
@@ -14451,7 +14451,7 @@
         <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="s">
         <v>747</v>
@@ -15027,7 +15027,7 @@
         <v>1240</v>
       </c>
       <c r="I29" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1" t="s">
@@ -15057,7 +15057,7 @@
         <v>1324</v>
       </c>
       <c r="H30" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>467</v>
@@ -15089,7 +15089,7 @@
         <v>1325</v>
       </c>
       <c r="H31" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="N31" t="s">
         <v>809</v>
@@ -15147,7 +15147,7 @@
         <v>1327</v>
       </c>
       <c r="H33" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>468</v>
@@ -15331,7 +15331,7 @@
         <v>1243</v>
       </c>
       <c r="J39" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>827</v>
@@ -15360,7 +15360,7 @@
         <v>1333</v>
       </c>
       <c r="H40" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>471</v>
@@ -15588,7 +15588,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B49">
         <v>906</v>
@@ -15606,7 +15606,7 @@
         <v>767</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>845</v>
@@ -15662,7 +15662,7 @@
         <v>1340</v>
       </c>
       <c r="H51" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>475</v>
@@ -15694,7 +15694,7 @@
         <v>1341</v>
       </c>
       <c r="H52" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>476</v>
@@ -15784,7 +15784,7 @@
         <v>1245</v>
       </c>
       <c r="I55" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>857</v>
@@ -15813,7 +15813,7 @@
         <v>1345</v>
       </c>
       <c r="H56" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N56" t="s">
         <v>859</v>
@@ -16167,7 +16167,7 @@
         <v>760</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="N69" t="s">
         <v>888</v>
@@ -16196,7 +16196,7 @@
         <v>760</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="N70" t="s">
         <v>891</v>
@@ -16309,7 +16309,7 @@
         <v>1361</v>
       </c>
       <c r="H74" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>899</v>
@@ -16338,7 +16338,7 @@
         <v>767</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>901</v>
@@ -16507,10 +16507,10 @@
         <v>1367</v>
       </c>
       <c r="H81" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I81" t="s">
         <v>1523</v>
-      </c>
-      <c r="I81" t="s">
-        <v>1524</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>746</v>
@@ -16658,7 +16658,7 @@
         <v>1246</v>
       </c>
       <c r="I86" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1" t="s">
@@ -16688,7 +16688,7 @@
         <v>1373</v>
       </c>
       <c r="H87" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>925</v>
@@ -16746,7 +16746,7 @@
         <v>749</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>482</v>
@@ -16919,7 +16919,7 @@
         <v>1380</v>
       </c>
       <c r="H95" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1" t="s">
@@ -17097,10 +17097,10 @@
         <v>1249</v>
       </c>
       <c r="I101" t="s">
+        <v>1531</v>
+      </c>
+      <c r="J101" t="s">
         <v>1532</v>
-      </c>
-      <c r="J101" t="s">
-        <v>1533</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>952</v>
@@ -17210,7 +17210,7 @@
         <v>1250</v>
       </c>
       <c r="I105" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="O105" s="1" t="s">
         <v>959</v>
@@ -17294,7 +17294,7 @@
         <v>760</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="O108" s="1" t="s">
         <v>965</v>
@@ -17665,7 +17665,7 @@
         <v>767</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>1396</v>
+        <v>1583</v>
       </c>
       <c r="O122" s="13" t="s">
         <v>988</v>
@@ -17691,7 +17691,7 @@
         <v>749</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1" t="s">
@@ -17718,7 +17718,7 @@
         <v>749</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="N124" t="s">
         <v>992</v>
@@ -17747,16 +17747,16 @@
         <v>749</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H125" t="s">
         <v>1257</v>
       </c>
       <c r="I125" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J125" t="s">
         <v>1525</v>
-      </c>
-      <c r="J125" t="s">
-        <v>1526</v>
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1" t="s">
@@ -17783,10 +17783,10 @@
         <v>749</v>
       </c>
       <c r="G126" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H126" t="s">
         <v>1564</v>
-      </c>
-      <c r="H126" t="s">
-        <v>1565</v>
       </c>
       <c r="N126" t="s">
         <v>997</v>
@@ -17815,7 +17815,7 @@
         <v>749</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="N127" t="s">
         <v>1000</v>
@@ -17844,7 +17844,7 @@
         <v>749</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="N128" s="1" t="s">
         <v>485</v>
@@ -17873,7 +17873,7 @@
         <v>749</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H129" t="s">
         <v>1258</v>
@@ -17882,10 +17882,10 @@
         <v>1259</v>
       </c>
       <c r="J129" t="s">
+        <v>1565</v>
+      </c>
+      <c r="K129" t="s">
         <v>1566</v>
-      </c>
-      <c r="K129" t="s">
-        <v>1567</v>
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1" t="s">
@@ -17912,7 +17912,7 @@
         <v>767</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>1006</v>
@@ -17944,10 +17944,10 @@
         <v>1260</v>
       </c>
       <c r="I131" t="s">
+        <v>1529</v>
+      </c>
+      <c r="J131" t="s">
         <v>1530</v>
-      </c>
-      <c r="J131" t="s">
-        <v>1531</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>1008</v>
@@ -18000,7 +18000,7 @@
         <v>749</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="N133" t="s">
         <v>1012</v>
@@ -18029,16 +18029,16 @@
         <v>749</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H134" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I134" t="s">
         <v>1527</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>1528</v>
-      </c>
-      <c r="J134" t="s">
-        <v>1529</v>
       </c>
       <c r="N134" t="s">
         <v>1014</v>
@@ -18067,7 +18067,7 @@
         <v>749</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="N135" s="1" t="s">
         <v>486</v>
@@ -18096,7 +18096,7 @@
         <v>767</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="N136" t="s">
         <v>1018</v>
@@ -18125,7 +18125,7 @@
         <v>749</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="O137" s="1" t="s">
         <v>1021</v>
@@ -18151,13 +18151,13 @@
         <v>749</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H138" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="I138" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="N138" t="s">
         <v>1023</v>
@@ -18186,7 +18186,7 @@
         <v>749</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H139" t="s">
         <v>1261</v>
@@ -18216,7 +18216,7 @@
         <v>749</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H140" t="s">
         <v>1262</v>
@@ -18246,7 +18246,7 @@
         <v>749</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H141" t="s">
         <v>1263</v>
@@ -18275,7 +18275,7 @@
         <v>749</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H142" t="s">
         <v>1264</v>
@@ -18305,7 +18305,7 @@
         <v>767</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="N143" t="s">
         <v>1034</v>
@@ -18334,16 +18334,16 @@
         <v>760</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H144" t="s">
+        <v>1539</v>
+      </c>
+      <c r="I144" t="s">
         <v>1540</v>
       </c>
-      <c r="I144" t="s">
-        <v>1541</v>
-      </c>
       <c r="J144" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="N144" t="s">
         <v>1037</v>
@@ -18372,7 +18372,7 @@
         <v>749</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>1039</v>
@@ -18398,7 +18398,7 @@
         <v>749</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="N146" t="s">
         <v>1041</v>
@@ -18427,7 +18427,7 @@
         <v>749</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1" t="s">
@@ -18454,25 +18454,25 @@
         <v>749</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H148" t="s">
         <v>1265</v>
       </c>
       <c r="I148" t="s">
+        <v>1550</v>
+      </c>
+      <c r="J148" t="s">
         <v>1551</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>1552</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" t="s">
         <v>1553</v>
       </c>
-      <c r="L148" t="s">
+      <c r="M148" t="s">
         <v>1554</v>
-      </c>
-      <c r="M148" t="s">
-        <v>1555</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>504</v>
@@ -18498,7 +18498,7 @@
         <v>760</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H149" t="s">
         <v>1266</v>
@@ -18527,7 +18527,7 @@
         <v>749</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H150" t="s">
         <v>1267</v>
@@ -18536,7 +18536,7 @@
         <v>1276</v>
       </c>
       <c r="J150" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>1049</v>
@@ -18562,10 +18562,10 @@
         <v>749</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H151" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="N151" t="s">
         <v>1051</v>
@@ -18594,10 +18594,10 @@
         <v>749</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H152" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>497</v>
@@ -18623,19 +18623,19 @@
         <v>760</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H153" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="I153" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="J153" t="s">
+        <v>1502</v>
+      </c>
+      <c r="K153" t="s">
         <v>1503</v>
-      </c>
-      <c r="K153" t="s">
-        <v>1504</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>1054</v>
@@ -18664,16 +18664,16 @@
         <v>1056</v>
       </c>
       <c r="H154" t="s">
+        <v>1577</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1498</v>
+      </c>
+      <c r="J154" t="s">
         <v>1578</v>
       </c>
-      <c r="I154" t="s">
-        <v>1499</v>
-      </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>1579</v>
-      </c>
-      <c r="K154" t="s">
-        <v>1580</v>
       </c>
       <c r="O154" s="1" t="s">
         <v>1056</v>
@@ -18707,13 +18707,13 @@
     </row>
     <row r="156" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="7" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B156" s="8">
         <v>2704</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>747</v>
@@ -18725,13 +18725,13 @@
         <v>749</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="O156" s="7" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
@@ -18754,16 +18754,16 @@
         <v>749</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>1268</v>
       </c>
       <c r="I157" s="10" t="s">
+        <v>1541</v>
+      </c>
+      <c r="J157" s="10" t="s">
         <v>1542</v>
-      </c>
-      <c r="J157" s="10" t="s">
-        <v>1543</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>1061</v>
@@ -18771,13 +18771,13 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B158" s="10">
         <v>2701</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>747</v>
@@ -18789,19 +18789,19 @@
         <v>749</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H158" s="10" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="I158" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>1574</v>
+      </c>
+      <c r="O158" s="9" t="s">
         <v>1572</v>
-      </c>
-      <c r="J158" s="10" t="s">
-        <v>1575</v>
-      </c>
-      <c r="O158" s="9" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="159" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
@@ -18824,10 +18824,10 @@
         <v>767</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="O159" s="7" t="s">
         <v>1063</v>
@@ -18853,7 +18853,7 @@
         <v>760</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>1269</v>
@@ -18864,7 +18864,7 @@
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A161" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B161">
         <v>2801</v>
@@ -18882,7 +18882,7 @@
         <v>749</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="O161" s="1" t="s">
         <v>1066</v>
@@ -18908,7 +18908,7 @@
         <v>749</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="N162" s="1"/>
       <c r="O162" s="1" t="s">
@@ -18935,13 +18935,13 @@
         <v>749</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H163" t="s">
         <v>1270</v>
       </c>
       <c r="I163" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>1069</v>
@@ -18967,7 +18967,7 @@
         <v>749</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>1071</v>
@@ -18993,7 +18993,7 @@
         <v>749</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>1073</v>
@@ -19019,7 +19019,7 @@
         <v>760</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="N166" s="1"/>
       <c r="O166" s="1" t="s">
@@ -19075,7 +19075,7 @@
         <v>749</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="N168" s="1"/>
       <c r="O168" s="1" t="s">
@@ -19102,7 +19102,7 @@
         <v>749</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H169" t="s">
         <v>1271</v>
@@ -19158,7 +19158,7 @@
         <v>749</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H171" t="s">
         <v>1272</v>
@@ -19187,7 +19187,7 @@
         <v>749</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H172" t="s">
         <v>1228</v>
@@ -19219,10 +19219,10 @@
         <v>760</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H173" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="N173" s="1"/>
       <c r="O173" s="1" t="s">
@@ -19278,7 +19278,7 @@
         <v>749</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="N175" t="s">
         <v>1096</v>
@@ -19307,16 +19307,16 @@
         <v>749</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H176" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I176" t="s">
         <v>1534</v>
       </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>1535</v>
-      </c>
-      <c r="J176" t="s">
-        <v>1536</v>
       </c>
       <c r="N176" s="1"/>
       <c r="O176" s="1" t="s">
@@ -19372,7 +19372,7 @@
         <v>749</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>498</v>
@@ -19398,7 +19398,7 @@
         <v>760</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="N179" t="s">
         <v>1104</v>
@@ -19427,7 +19427,7 @@
         <v>760</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H180" t="s">
         <v>1297</v>
@@ -19456,7 +19456,7 @@
         <v>749</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H181" t="s">
         <v>1274</v>
@@ -19489,10 +19489,10 @@
         <v>1228</v>
       </c>
       <c r="I182" t="s">
+        <v>1556</v>
+      </c>
+      <c r="J182" t="s">
         <v>1557</v>
-      </c>
-      <c r="J182" t="s">
-        <v>1558</v>
       </c>
       <c r="N182" t="s">
         <v>269</v>
@@ -19540,7 +19540,7 @@
         <v>749</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H184" t="s">
         <v>1228</v>
@@ -19549,10 +19549,10 @@
         <v>1277</v>
       </c>
       <c r="J184" t="s">
+        <v>1544</v>
+      </c>
+      <c r="K184" t="s">
         <v>1545</v>
-      </c>
-      <c r="K184" t="s">
-        <v>1546</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>507</v>
@@ -19578,22 +19578,22 @@
         <v>749</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H185" t="s">
         <v>1278</v>
       </c>
       <c r="I185" t="s">
+        <v>1546</v>
+      </c>
+      <c r="J185" t="s">
         <v>1547</v>
       </c>
-      <c r="J185" t="s">
+      <c r="K185" t="s">
         <v>1548</v>
       </c>
-      <c r="K185" t="s">
+      <c r="L185" t="s">
         <v>1549</v>
-      </c>
-      <c r="L185" t="s">
-        <v>1550</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>508</v>
@@ -19619,7 +19619,7 @@
         <v>767</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H186" t="s">
         <v>1275</v>
@@ -19648,7 +19648,7 @@
         <v>749</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="O187" s="1"/>
     </row>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\星杯传说工程\星杯传说2\xianyu_xingbei\Table\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205EB1C9-CEA2-42D6-A2F7-4AF4A26CB843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F53B6C8-1C77-46A5-9026-0C2744FB1196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>
@@ -3462,10 +3462,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>（仅【审判形态】下发动）↻脱离【审判形态】，我方【战绩区】+1【宝石】。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>末日审判</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5904,9 +5900,6 @@
     <t>发动【黄泉震颤】：补满手牌后请弃 2 张牌</t>
   </si>
   <si>
-    <t>发动【冒险者天堂】：先选本次提炼的总颗数，再点头像把星石分给队友（最多 2 名）</t>
-  </si>
-  <si>
     <t>发动【偷天换日】：转移对方 1 宝石 或 把我方【战绩区】水晶全部转为宝石</t>
   </si>
   <si>
@@ -5992,13 +5985,43 @@
   </si>
   <si>
     <t>【英灵召唤】：目标角色+1【治疗】</t>
+  </si>
+  <si>
+    <t>发动【冒险者天堂】：选择额外提取数量</t>
+  </si>
+  <si>
+    <r>
+      <t>（仅【审判形态】下发动）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【重置】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>脱离【审判形态】，我方【战绩区】+1【宝石】。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6078,6 +6101,21 @@
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -6406,7 +6444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5839A4A7-E3EE-408B-ABC6-26D91AFB7BC6}">
   <dimension ref="A1:T42"/>
-  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.06640625" style="4"/>
@@ -6429,15 +6467,15 @@
     <col min="20" max="20" width="129.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1">
+    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>344</v>
@@ -6464,10 +6502,10 @@
         <v>446</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>270</v>
@@ -6476,7 +6514,7 @@
         <v>106</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>367</v>
@@ -6491,15 +6529,15 @@
         <v>373</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>345</v>
@@ -6526,10 +6564,10 @@
         <v>447</v>
       </c>
       <c r="L2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>271</v>
@@ -6538,7 +6576,7 @@
         <v>9</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="Q2" t="s">
         <v>368</v>
@@ -6553,12 +6591,12 @@
         <v>374</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -6591,7 +6629,7 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>110</v>
@@ -6612,15 +6650,15 @@
         <v>15</v>
       </c>
       <c r="T3" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6653,15 +6691,15 @@
         <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6694,7 +6732,7 @@
         <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>279</v>
@@ -6703,15 +6741,15 @@
         <v>375</v>
       </c>
       <c r="T5" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -6744,7 +6782,7 @@
         <v>38</v>
       </c>
       <c r="P6" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>280</v>
@@ -6753,15 +6791,15 @@
         <v>376</v>
       </c>
       <c r="T6" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -6794,7 +6832,7 @@
         <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>281</v>
@@ -6803,15 +6841,15 @@
         <v>377</v>
       </c>
       <c r="T7" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -6844,7 +6882,7 @@
         <v>19</v>
       </c>
       <c r="P8" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>282</v>
@@ -6853,15 +6891,15 @@
         <v>378</v>
       </c>
       <c r="T8" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -6891,10 +6929,10 @@
         <v>448</v>
       </c>
       <c r="L9" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="M9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>284</v>
@@ -6903,7 +6941,7 @@
         <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>284</v>
@@ -6912,15 +6950,15 @@
         <v>379</v>
       </c>
       <c r="T9" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -6950,10 +6988,10 @@
         <v>449</v>
       </c>
       <c r="L10" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="M10" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>286</v>
@@ -6962,7 +7000,7 @@
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q10" s="1" t="s">
         <v>286</v>
@@ -6971,15 +7009,15 @@
         <v>380</v>
       </c>
       <c r="T10" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -7012,7 +7050,7 @@
         <v>24</v>
       </c>
       <c r="P11" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>287</v>
@@ -7021,15 +7059,15 @@
         <v>381</v>
       </c>
       <c r="T11" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -7062,7 +7100,7 @@
         <v>26</v>
       </c>
       <c r="P12" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>288</v>
@@ -7071,15 +7109,15 @@
         <v>382</v>
       </c>
       <c r="T12" t="s">
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -7109,10 +7147,10 @@
         <v>450</v>
       </c>
       <c r="L13" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="M13" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>291</v>
@@ -7121,7 +7159,7 @@
         <v>19</v>
       </c>
       <c r="P13" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>291</v>
@@ -7130,15 +7168,15 @@
         <v>383</v>
       </c>
       <c r="T13" t="s">
-        <v>1466</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -7171,7 +7209,7 @@
         <v>24</v>
       </c>
       <c r="P14" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>292</v>
@@ -7180,15 +7218,15 @@
         <v>384</v>
       </c>
       <c r="T14" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -7221,7 +7259,7 @@
         <v>26</v>
       </c>
       <c r="P15" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>293</v>
@@ -7233,15 +7271,15 @@
         <v>386</v>
       </c>
       <c r="T15" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -7268,13 +7306,13 @@
         <v>23</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="O16" t="s">
         <v>19</v>
       </c>
       <c r="P16" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>295</v>
@@ -7283,15 +7321,15 @@
         <v>387</v>
       </c>
       <c r="T16" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -7324,7 +7362,7 @@
         <v>19</v>
       </c>
       <c r="P17" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>296</v>
@@ -7333,15 +7371,15 @@
         <v>388</v>
       </c>
       <c r="T17" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -7371,10 +7409,10 @@
         <v>451</v>
       </c>
       <c r="L18" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M18" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>299</v>
@@ -7383,7 +7421,7 @@
         <v>38</v>
       </c>
       <c r="P18" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>299</v>
@@ -7395,15 +7433,15 @@
         <v>390</v>
       </c>
       <c r="T18" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -7436,7 +7474,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>300</v>
@@ -7445,15 +7483,15 @@
         <v>391</v>
       </c>
       <c r="T19" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -7483,10 +7521,10 @@
         <v>452</v>
       </c>
       <c r="L20" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="M20" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>302</v>
@@ -7495,7 +7533,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>302</v>
@@ -7507,15 +7545,15 @@
         <v>393</v>
       </c>
       <c r="T20" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C21">
         <v>17</v>
@@ -7548,7 +7586,7 @@
         <v>26</v>
       </c>
       <c r="P21" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>304</v>
@@ -7557,15 +7595,15 @@
         <v>394</v>
       </c>
       <c r="T21" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -7598,7 +7636,7 @@
         <v>26</v>
       </c>
       <c r="P22" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>305</v>
@@ -7610,15 +7648,15 @@
         <v>396</v>
       </c>
       <c r="T22" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C23">
         <v>19</v>
@@ -7651,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="P23" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>306</v>
@@ -7663,15 +7701,15 @@
         <v>398</v>
       </c>
       <c r="T23" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -7701,10 +7739,10 @@
         <v>453</v>
       </c>
       <c r="L24" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="M24" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>308</v>
@@ -7713,7 +7751,7 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>308</v>
@@ -7725,15 +7763,15 @@
         <v>400</v>
       </c>
       <c r="T24" t="s">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C25">
         <v>21</v>
@@ -7763,10 +7801,10 @@
         <v>454</v>
       </c>
       <c r="L25" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M25" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>311</v>
@@ -7775,7 +7813,7 @@
         <v>38</v>
       </c>
       <c r="P25" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>311</v>
@@ -7787,15 +7825,15 @@
         <v>402</v>
       </c>
       <c r="T25" t="s">
-        <v>1552</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C26">
         <v>22</v>
@@ -7828,7 +7866,7 @@
         <v>19</v>
       </c>
       <c r="P26" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>312</v>
@@ -7840,15 +7878,15 @@
         <v>404</v>
       </c>
       <c r="T26" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C27">
         <v>23</v>
@@ -7878,10 +7916,10 @@
         <v>455</v>
       </c>
       <c r="L27" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M27" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>314</v>
@@ -7890,7 +7928,7 @@
         <v>38</v>
       </c>
       <c r="P27" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>314</v>
@@ -7899,15 +7937,15 @@
         <v>405</v>
       </c>
       <c r="T27" t="s">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C28">
         <v>24</v>
@@ -7937,10 +7975,10 @@
         <v>456</v>
       </c>
       <c r="L28" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="M28" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>318</v>
@@ -7949,7 +7987,7 @@
         <v>26</v>
       </c>
       <c r="P28" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>318</v>
@@ -7961,15 +7999,15 @@
         <v>407</v>
       </c>
       <c r="T28" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -7999,10 +8037,10 @@
         <v>457</v>
       </c>
       <c r="L29" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="M29" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>320</v>
@@ -8011,7 +8049,7 @@
         <v>24</v>
       </c>
       <c r="P29" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>320</v>
@@ -8020,15 +8058,15 @@
         <v>408</v>
       </c>
       <c r="T29" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -8061,7 +8099,7 @@
         <v>19</v>
       </c>
       <c r="P30" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>321</v>
@@ -8073,15 +8111,15 @@
         <v>410</v>
       </c>
       <c r="T30" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C31">
         <v>27</v>
@@ -8111,10 +8149,10 @@
         <v>458</v>
       </c>
       <c r="L31" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="M31" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>324</v>
@@ -8123,7 +8161,7 @@
         <v>26</v>
       </c>
       <c r="P31" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q31" s="1" t="s">
         <v>324</v>
@@ -8135,15 +8173,15 @@
         <v>412</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C32">
         <v>28</v>
@@ -8173,10 +8211,10 @@
         <v>459</v>
       </c>
       <c r="L32" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M32" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>326</v>
@@ -8185,7 +8223,7 @@
         <v>38</v>
       </c>
       <c r="P32" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q32" s="1" t="s">
         <v>326</v>
@@ -8197,15 +8235,15 @@
         <v>414</v>
       </c>
       <c r="T32" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C33">
         <v>29</v>
@@ -8235,10 +8273,10 @@
         <v>460</v>
       </c>
       <c r="L33" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="M33" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>329</v>
@@ -8247,7 +8285,7 @@
         <v>19</v>
       </c>
       <c r="P33" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q33" s="1" t="s">
         <v>329</v>
@@ -8256,15 +8294,15 @@
         <v>415</v>
       </c>
       <c r="T33" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C34">
         <v>30</v>
@@ -8294,10 +8332,10 @@
         <v>461</v>
       </c>
       <c r="L34" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M34" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>332</v>
@@ -8306,7 +8344,7 @@
         <v>38</v>
       </c>
       <c r="P34" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q34" s="1" t="s">
         <v>332</v>
@@ -8318,15 +8356,15 @@
         <v>417</v>
       </c>
       <c r="T34" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -8356,10 +8394,10 @@
         <v>434</v>
       </c>
       <c r="L35" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="M35" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>334</v>
@@ -8368,7 +8406,7 @@
         <v>19</v>
       </c>
       <c r="P35" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>334</v>
@@ -8380,15 +8418,15 @@
         <v>419</v>
       </c>
       <c r="T35" t="s">
-        <v>1554</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -8418,10 +8456,10 @@
         <v>462</v>
       </c>
       <c r="L36" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="M36" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>337</v>
@@ -8430,7 +8468,7 @@
         <v>27</v>
       </c>
       <c r="P36" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>337</v>
@@ -8442,15 +8480,15 @@
         <v>421</v>
       </c>
       <c r="T36" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C37">
         <v>33</v>
@@ -8480,10 +8518,10 @@
         <v>434</v>
       </c>
       <c r="L37" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="M37" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>435</v>
@@ -8492,7 +8530,7 @@
         <v>38</v>
       </c>
       <c r="P37" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="Q37" s="1" t="s">
         <v>435</v>
@@ -8504,15 +8542,15 @@
         <v>437</v>
       </c>
       <c r="T37" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C38">
         <v>34</v>
@@ -8542,10 +8580,10 @@
         <v>463</v>
       </c>
       <c r="L38" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="M38" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>339</v>
@@ -8554,7 +8592,7 @@
         <v>24</v>
       </c>
       <c r="P38" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>339</v>
@@ -8566,15 +8604,15 @@
         <v>423</v>
       </c>
       <c r="T38" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C39">
         <v>35</v>
@@ -8604,10 +8642,10 @@
         <v>430</v>
       </c>
       <c r="L39" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="M39" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>341</v>
@@ -8616,7 +8654,7 @@
         <v>27</v>
       </c>
       <c r="P39" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>341</v>
@@ -8628,15 +8666,15 @@
         <v>425</v>
       </c>
       <c r="T39" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C40">
         <v>36</v>
@@ -8666,10 +8704,10 @@
         <v>448</v>
       </c>
       <c r="L40" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="M40" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>343</v>
@@ -8678,7 +8716,7 @@
         <v>24</v>
       </c>
       <c r="P40" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>343</v>
@@ -8690,15 +8728,15 @@
         <v>427</v>
       </c>
       <c r="T40" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C41">
         <v>37</v>
@@ -8728,7 +8766,7 @@
         <v>430</v>
       </c>
       <c r="L41" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>431</v>
@@ -8737,7 +8775,7 @@
         <v>464</v>
       </c>
       <c r="P41" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="Q41" s="1" t="s">
         <v>431</v>
@@ -8749,15 +8787,15 @@
         <v>433</v>
       </c>
       <c r="T41" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C42">
         <v>108</v>
@@ -8784,7 +8822,7 @@
         <v>26</v>
       </c>
       <c r="P42" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="Q42" t="s">
         <v>444</v>
@@ -8805,7 +8843,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7A31B9-DA13-42EA-9657-5BB3EA92E677}">
   <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
@@ -8819,7 +8857,7 @@
     <col min="11" max="11" width="255.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>109</v>
       </c>
@@ -8830,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -8854,7 +8892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -8889,7 +8927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -8912,10 +8950,10 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="I3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="J3" t="s">
         <v>272</v>
@@ -8924,7 +8962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -8959,7 +8997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -8994,7 +9032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -9029,7 +9067,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -9064,7 +9102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -9099,7 +9137,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -9134,7 +9172,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -9169,7 +9207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -9204,7 +9242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -9239,7 +9277,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>120</v>
       </c>
@@ -9274,7 +9312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -9309,7 +9347,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>122</v>
       </c>
@@ -9344,7 +9382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -9379,7 +9417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -9414,7 +9452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -9449,7 +9487,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -9484,7 +9522,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -9519,7 +9557,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>128</v>
       </c>
@@ -9554,7 +9592,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>129</v>
       </c>
@@ -9589,7 +9627,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>130</v>
       </c>
@@ -9624,7 +9662,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -9659,7 +9697,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -9694,7 +9732,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -9729,7 +9767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -9764,7 +9802,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -9799,7 +9837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -9834,7 +9872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -9869,7 +9907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>138</v>
       </c>
@@ -9904,7 +9942,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -9939,7 +9977,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -9974,7 +10012,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>141</v>
       </c>
@@ -10009,7 +10047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -10044,7 +10082,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>143</v>
       </c>
@@ -10079,7 +10117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>144</v>
       </c>
@@ -10114,7 +10152,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>145</v>
       </c>
@@ -10149,7 +10187,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -10184,7 +10222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -10219,7 +10257,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>148</v>
       </c>
@@ -10254,7 +10292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>149</v>
       </c>
@@ -10289,7 +10327,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -10324,7 +10362,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -10359,7 +10397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -10394,7 +10432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -10429,7 +10467,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>154</v>
       </c>
@@ -10464,7 +10502,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>155</v>
       </c>
@@ -10499,7 +10537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>156</v>
       </c>
@@ -10534,7 +10572,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -10569,7 +10607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -10604,7 +10642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -10639,7 +10677,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -10674,7 +10712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -10709,7 +10747,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -10744,7 +10782,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -10779,7 +10817,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>164</v>
       </c>
@@ -10814,7 +10852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -10849,7 +10887,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>166</v>
       </c>
@@ -10884,7 +10922,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>167</v>
       </c>
@@ -10919,7 +10957,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>168</v>
       </c>
@@ -10954,7 +10992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -10989,7 +11027,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>170</v>
       </c>
@@ -11024,7 +11062,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>171</v>
       </c>
@@ -11059,7 +11097,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>172</v>
       </c>
@@ -11094,7 +11132,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>173</v>
       </c>
@@ -11129,7 +11167,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>174</v>
       </c>
@@ -11164,7 +11202,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>175</v>
       </c>
@@ -11199,7 +11237,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>176</v>
       </c>
@@ -11234,7 +11272,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>177</v>
       </c>
@@ -11269,7 +11307,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>178</v>
       </c>
@@ -11304,7 +11342,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>179</v>
       </c>
@@ -11339,7 +11377,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>180</v>
       </c>
@@ -11374,7 +11412,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>181</v>
       </c>
@@ -11409,7 +11447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>182</v>
       </c>
@@ -11444,7 +11482,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>183</v>
       </c>
@@ -11479,7 +11517,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>184</v>
       </c>
@@ -11514,7 +11552,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>185</v>
       </c>
@@ -11549,7 +11587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>186</v>
       </c>
@@ -11584,7 +11622,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -11619,7 +11657,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -11654,7 +11692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>189</v>
       </c>
@@ -11689,7 +11727,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>190</v>
       </c>
@@ -11724,7 +11762,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>191</v>
       </c>
@@ -11759,7 +11797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>192</v>
       </c>
@@ -11794,7 +11832,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>193</v>
       </c>
@@ -11829,7 +11867,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>194</v>
       </c>
@@ -11864,7 +11902,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>195</v>
       </c>
@@ -11899,7 +11937,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -11934,7 +11972,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -11969,7 +12007,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -12004,7 +12042,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>199</v>
       </c>
@@ -12039,7 +12077,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>200</v>
       </c>
@@ -12074,7 +12112,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -12109,7 +12147,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>202</v>
       </c>
@@ -12144,7 +12182,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -12179,7 +12217,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -12214,7 +12252,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -12249,7 +12287,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>206</v>
       </c>
@@ -12284,7 +12322,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>207</v>
       </c>
@@ -12319,7 +12357,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>208</v>
       </c>
@@ -12354,7 +12392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -12389,7 +12427,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -12424,7 +12462,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>211</v>
       </c>
@@ -12459,7 +12497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>212</v>
       </c>
@@ -12494,7 +12532,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -12529,7 +12567,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -12564,7 +12602,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -12599,7 +12637,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -12634,7 +12672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>217</v>
       </c>
@@ -12669,7 +12707,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -12704,7 +12742,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>219</v>
       </c>
@@ -12739,7 +12777,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>220</v>
       </c>
@@ -12774,7 +12812,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>221</v>
       </c>
@@ -12809,7 +12847,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>222</v>
       </c>
@@ -12844,7 +12882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -12879,7 +12917,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>224</v>
       </c>
@@ -12914,7 +12952,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>225</v>
       </c>
@@ -12949,7 +12987,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>226</v>
       </c>
@@ -12984,7 +13022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>227</v>
       </c>
@@ -13019,7 +13057,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>228</v>
       </c>
@@ -13054,7 +13092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>229</v>
       </c>
@@ -13089,7 +13127,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>230</v>
       </c>
@@ -13124,7 +13162,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>231</v>
       </c>
@@ -13159,7 +13197,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>232</v>
       </c>
@@ -13194,7 +13232,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>233</v>
       </c>
@@ -13229,7 +13267,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>234</v>
       </c>
@@ -13264,7 +13302,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>235</v>
       </c>
@@ -13299,7 +13337,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>236</v>
       </c>
@@ -13334,7 +13372,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>237</v>
       </c>
@@ -13369,7 +13407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>238</v>
       </c>
@@ -13404,7 +13442,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>239</v>
       </c>
@@ -13439,7 +13477,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -13474,7 +13512,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>241</v>
       </c>
@@ -13509,7 +13547,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>242</v>
       </c>
@@ -13544,7 +13582,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>243</v>
       </c>
@@ -13579,7 +13617,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -13614,7 +13652,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>245</v>
       </c>
@@ -13649,7 +13687,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>246</v>
       </c>
@@ -13684,7 +13722,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>247</v>
       </c>
@@ -13719,7 +13757,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>248</v>
       </c>
@@ -13754,7 +13792,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>249</v>
       </c>
@@ -13789,7 +13827,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>250</v>
       </c>
@@ -13824,7 +13862,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>251</v>
       </c>
@@ -13859,7 +13897,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>252</v>
       </c>
@@ -13894,7 +13932,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -13929,7 +13967,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>254</v>
       </c>
@@ -13964,7 +14002,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>255</v>
       </c>
@@ -13999,7 +14037,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>256</v>
       </c>
@@ -14034,7 +14072,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>257</v>
       </c>
@@ -14069,7 +14107,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>258</v>
       </c>
@@ -14104,7 +14142,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>259</v>
       </c>
@@ -14139,7 +14177,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>260</v>
       </c>
@@ -14174,7 +14212,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>261</v>
       </c>
@@ -14209,7 +14247,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>262</v>
       </c>
@@ -14244,7 +14282,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>263</v>
       </c>
@@ -14279,7 +14317,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>264</v>
       </c>
@@ -14314,7 +14352,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>265</v>
       </c>
@@ -14358,7 +14396,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064C6D04-9B4F-44DE-8444-798F1E3ED691}">
   <dimension ref="A1:O233"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.86328125" customWidth="1"/>
     <col min="2" max="2" width="8.06640625" bestFit="1" customWidth="1"/>
@@ -14368,7 +14406,7 @@
     <col min="15" max="15" width="20.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -14388,25 +14426,25 @@
         <v>358</v>
       </c>
       <c r="G1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L1" t="s">
         <v>1487</v>
       </c>
-      <c r="H1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1485</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1488</v>
-      </c>
       <c r="M1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N1" t="s">
         <v>438</v>
@@ -14415,7 +14453,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -14438,22 +14476,22 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="I2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="L2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="M2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="N2" t="s">
         <v>439</v>
@@ -14462,7 +14500,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -14485,22 +14523,22 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="I3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="J3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="K3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="L3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="M3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="N3" t="s">
         <v>15</v>
@@ -14509,9 +14547,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B4">
         <v>103</v>
@@ -14535,7 +14573,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>528</v>
       </c>
@@ -14558,16 +14596,16 @@
         <v>752</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>1555</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>1556</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>527</v>
       </c>
@@ -14590,10 +14628,10 @@
         <v>755</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>526</v>
       </c>
@@ -14616,10 +14654,10 @@
         <v>757</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>529</v>
       </c>
@@ -14627,7 +14665,7 @@
         <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D8" t="s">
         <v>746</v>
@@ -14642,10 +14680,10 @@
         <v>760</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>532</v>
       </c>
@@ -14668,10 +14706,10 @@
         <v>762</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>530</v>
       </c>
@@ -14694,10 +14732,10 @@
         <v>499</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>531</v>
       </c>
@@ -14717,13 +14755,13 @@
         <v>748</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>533</v>
       </c>
@@ -14746,10 +14784,10 @@
         <v>767</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>537</v>
       </c>
@@ -14772,10 +14810,10 @@
         <v>769</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>538</v>
       </c>
@@ -14798,13 +14836,13 @@
         <v>771</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>535</v>
       </c>
@@ -14827,10 +14865,10 @@
         <v>774</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>534</v>
       </c>
@@ -14853,10 +14891,10 @@
         <v>776</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>536</v>
       </c>
@@ -14879,10 +14917,10 @@
         <v>778</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>544</v>
       </c>
@@ -14905,10 +14943,10 @@
         <v>780</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>542</v>
       </c>
@@ -14931,10 +14969,10 @@
         <v>782</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>540</v>
       </c>
@@ -14957,10 +14995,10 @@
         <v>784</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>541</v>
       </c>
@@ -14983,10 +15021,10 @@
         <v>786</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>539</v>
       </c>
@@ -15009,10 +15047,10 @@
         <v>788</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>543</v>
       </c>
@@ -15035,10 +15073,10 @@
         <v>790</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>545</v>
       </c>
@@ -15061,16 +15099,16 @@
         <v>793</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>465</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>546</v>
       </c>
@@ -15096,10 +15134,10 @@
         <v>466</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>547</v>
       </c>
@@ -15122,10 +15160,10 @@
         <v>797</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>548</v>
       </c>
@@ -15148,16 +15186,16 @@
         <v>799</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>1559</v>
-      </c>
       <c r="O27" s="1" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>549</v>
       </c>
@@ -15180,13 +15218,13 @@
         <v>802</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>552</v>
       </c>
@@ -15209,17 +15247,17 @@
         <v>804</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>550</v>
       </c>
@@ -15242,16 +15280,16 @@
         <v>806</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>467</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>551</v>
       </c>
@@ -15274,16 +15312,16 @@
         <v>809</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="N31" t="s">
         <v>808</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>553</v>
       </c>
@@ -15306,10 +15344,10 @@
         <v>811</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>554</v>
       </c>
@@ -15332,16 +15370,16 @@
         <v>813</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>468</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>557</v>
       </c>
@@ -15367,10 +15405,10 @@
         <v>470</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>556</v>
       </c>
@@ -15393,16 +15431,16 @@
         <v>817</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>469</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>558</v>
       </c>
@@ -15425,14 +15463,14 @@
         <v>819</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>555</v>
       </c>
@@ -15461,7 +15499,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>559</v>
       </c>
@@ -15484,13 +15522,13 @@
         <v>824</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>560</v>
       </c>
@@ -15513,16 +15551,16 @@
         <v>826</v>
       </c>
       <c r="H39" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>1562</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>1563</v>
-      </c>
       <c r="O39" s="1" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>561</v>
       </c>
@@ -15545,16 +15583,16 @@
         <v>828</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>471</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>562</v>
       </c>
@@ -15580,7 +15618,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>563</v>
       </c>
@@ -15609,7 +15647,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>564</v>
       </c>
@@ -15635,10 +15673,10 @@
         <v>473</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>565</v>
       </c>
@@ -15661,10 +15699,10 @@
         <v>835</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>566</v>
       </c>
@@ -15687,10 +15725,10 @@
         <v>837</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>567</v>
       </c>
@@ -15713,10 +15751,10 @@
         <v>839</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>568</v>
       </c>
@@ -15742,7 +15780,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>569</v>
       </c>
@@ -15765,21 +15803,21 @@
         <v>843</v>
       </c>
       <c r="H48" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>1565</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>1566</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>474</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B49">
         <v>906</v>
@@ -15800,13 +15838,13 @@
         <v>844</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>575</v>
       </c>
@@ -15830,10 +15868,10 @@
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>570</v>
       </c>
@@ -15856,16 +15894,16 @@
         <v>848</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>475</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>571</v>
       </c>
@@ -15888,16 +15926,16 @@
         <v>850</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>476</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>576</v>
       </c>
@@ -15920,10 +15958,10 @@
         <v>852</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>573</v>
       </c>
@@ -15946,13 +15984,13 @@
         <v>854</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>574</v>
       </c>
@@ -15975,16 +16013,16 @@
         <v>856</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>572</v>
       </c>
@@ -16007,16 +16045,16 @@
         <v>859</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="N56" t="s">
         <v>858</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>584</v>
       </c>
@@ -16039,10 +16077,10 @@
         <v>861</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>582</v>
       </c>
@@ -16068,10 +16106,10 @@
         <v>863</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>580</v>
       </c>
@@ -16094,10 +16132,10 @@
         <v>866</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>578</v>
       </c>
@@ -16120,10 +16158,10 @@
         <v>868</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>579</v>
       </c>
@@ -16146,10 +16184,10 @@
         <v>870</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>577</v>
       </c>
@@ -16173,10 +16211,10 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>581</v>
       </c>
@@ -16200,10 +16238,10 @@
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>583</v>
       </c>
@@ -16229,10 +16267,10 @@
         <v>876</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>585</v>
       </c>
@@ -16258,10 +16296,10 @@
         <v>477</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>880</v>
       </c>
@@ -16284,10 +16322,10 @@
         <v>882</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>883</v>
       </c>
@@ -16311,10 +16349,10 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>586</v>
       </c>
@@ -16336,17 +16374,15 @@
       <c r="G68" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发动【冒险者天堂】：选择额外提取数量</t>
-        </is>
+      <c r="H68" s="1" t="s">
+        <v>1595</v>
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>587</v>
       </c>
@@ -16369,16 +16405,16 @@
         <v>888</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="N69" t="s">
         <v>887</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>588</v>
       </c>
@@ -16402,10 +16438,10 @@
         <v>890</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>589</v>
       </c>
@@ -16429,10 +16465,10 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>590</v>
       </c>
@@ -16456,10 +16492,10 @@
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>591</v>
       </c>
@@ -16485,10 +16521,10 @@
         <v>478</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>592</v>
       </c>
@@ -16511,16 +16547,16 @@
         <v>899</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>898</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>593</v>
       </c>
@@ -16546,10 +16582,10 @@
         <v>900</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>902</v>
       </c>
@@ -16573,10 +16609,10 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
         <v>594</v>
       </c>
@@ -16596,14 +16632,14 @@
         <v>748</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>905</v>
+        <v>1596</v>
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>596</v>
       </c>
@@ -16611,7 +16647,7 @@
         <v>1403</v>
       </c>
       <c r="C78" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D78" t="s">
         <v>773</v>
@@ -16623,16 +16659,16 @@
         <v>748</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>479</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
         <v>597</v>
       </c>
@@ -16640,7 +16676,7 @@
         <v>1404</v>
       </c>
       <c r="C79" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D79" t="s">
         <v>751</v>
@@ -16652,14 +16688,14 @@
         <v>748</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>595</v>
       </c>
@@ -16667,7 +16703,7 @@
         <v>1402</v>
       </c>
       <c r="C80" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D80" t="s">
         <v>801</v>
@@ -16679,14 +16715,14 @@
         <v>766</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>598</v>
       </c>
@@ -16694,7 +16730,7 @@
         <v>1405</v>
       </c>
       <c r="C81" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D81" t="s">
         <v>773</v>
@@ -16709,19 +16745,19 @@
         <v>500</v>
       </c>
       <c r="H81" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>1501</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>1502</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>745</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>599</v>
       </c>
@@ -16729,7 +16765,7 @@
         <v>1501</v>
       </c>
       <c r="C82" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D82" t="s">
         <v>746</v>
@@ -16741,13 +16777,13 @@
         <v>748</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>600</v>
       </c>
@@ -16755,7 +16791,7 @@
         <v>1502</v>
       </c>
       <c r="C83" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D83" t="s">
         <v>773</v>
@@ -16767,16 +16803,16 @@
         <v>748</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N83" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>601</v>
       </c>
@@ -16784,7 +16820,7 @@
         <v>1503</v>
       </c>
       <c r="C84" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D84" t="s">
         <v>773</v>
@@ -16796,19 +16832,19 @@
         <v>748</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>480</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>602</v>
       </c>
@@ -16816,7 +16852,7 @@
         <v>1504</v>
       </c>
       <c r="C85" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D85" t="s">
         <v>364</v>
@@ -16831,10 +16867,10 @@
         <v>490</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>603</v>
       </c>
@@ -16842,7 +16878,7 @@
         <v>1505</v>
       </c>
       <c r="C86" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D86" t="s">
         <v>801</v>
@@ -16854,20 +16890,20 @@
         <v>759</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>604</v>
       </c>
@@ -16875,7 +16911,7 @@
         <v>1506</v>
       </c>
       <c r="C87" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D87" t="s">
         <v>773</v>
@@ -16890,16 +16926,16 @@
         <v>501</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>608</v>
       </c>
@@ -16907,7 +16943,7 @@
         <v>1604</v>
       </c>
       <c r="C88" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D88" t="s">
         <v>773</v>
@@ -16919,16 +16955,16 @@
         <v>748</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>481</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>609</v>
       </c>
@@ -16948,16 +16984,16 @@
         <v>748</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>482</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>606</v>
       </c>
@@ -16965,7 +17001,7 @@
         <v>1602</v>
       </c>
       <c r="C90" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D90" t="s">
         <v>773</v>
@@ -16977,19 +17013,19 @@
         <v>748</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="N90" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>605</v>
       </c>
@@ -16997,7 +17033,7 @@
         <v>1601</v>
       </c>
       <c r="C91" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D91" t="s">
         <v>773</v>
@@ -17009,16 +17045,16 @@
         <v>748</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="N91" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>607</v>
       </c>
@@ -17038,14 +17074,14 @@
         <v>766</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>610</v>
       </c>
@@ -17053,7 +17089,7 @@
         <v>1606</v>
       </c>
       <c r="C93" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D93" t="s">
         <v>746</v>
@@ -17065,14 +17101,14 @@
         <v>759</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>611</v>
       </c>
@@ -17080,7 +17116,7 @@
         <v>1701</v>
       </c>
       <c r="C94" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D94" t="s">
         <v>751</v>
@@ -17092,16 +17128,16 @@
         <v>748</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>614</v>
       </c>
@@ -17109,7 +17145,7 @@
         <v>1704</v>
       </c>
       <c r="C95" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D95" t="s">
         <v>361</v>
@@ -17121,17 +17157,17 @@
         <v>748</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>612</v>
       </c>
@@ -17139,7 +17175,7 @@
         <v>1702</v>
       </c>
       <c r="C96" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D96" t="s">
         <v>366</v>
@@ -17151,16 +17187,16 @@
         <v>766</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>483</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>613</v>
       </c>
@@ -17168,7 +17204,7 @@
         <v>1703</v>
       </c>
       <c r="C97" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D97" t="s">
         <v>773</v>
@@ -17180,16 +17216,16 @@
         <v>766</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="N97" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" s="6" customFormat="1">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
         <v>616</v>
       </c>
@@ -17209,16 +17245,16 @@
         <v>748</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="N98" s="6" t="s">
         <v>266</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" s="6" customFormat="1">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
         <v>615</v>
       </c>
@@ -17238,16 +17274,16 @@
         <v>748</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="N99" s="6" t="s">
         <v>267</v>
       </c>
       <c r="O99" s="5" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
         <v>617</v>
       </c>
@@ -17255,7 +17291,7 @@
         <v>1803</v>
       </c>
       <c r="C100" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D100" t="s">
         <v>746</v>
@@ -17267,16 +17303,16 @@
         <v>748</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
         <v>618</v>
       </c>
@@ -17284,7 +17320,7 @@
         <v>1804</v>
       </c>
       <c r="C101" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D101" t="s">
         <v>746</v>
@@ -17296,22 +17332,22 @@
         <v>748</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="I101" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="J101" s="1" t="s">
         <v>1510</v>
       </c>
-      <c r="J101" s="1" t="s">
-        <v>1511</v>
-      </c>
       <c r="O101" s="1" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
         <v>619</v>
       </c>
@@ -17319,7 +17355,7 @@
         <v>1805</v>
       </c>
       <c r="C102" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D102" t="s">
         <v>746</v>
@@ -17331,13 +17367,13 @@
         <v>759</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
         <v>620</v>
       </c>
@@ -17345,7 +17381,7 @@
         <v>1901</v>
       </c>
       <c r="C103" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D103" t="s">
         <v>364</v>
@@ -17363,7 +17399,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
         <v>621</v>
       </c>
@@ -17371,7 +17407,7 @@
         <v>1902</v>
       </c>
       <c r="C104" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D104" t="s">
         <v>751</v>
@@ -17383,13 +17419,13 @@
         <v>748</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
         <v>622</v>
       </c>
@@ -17397,7 +17433,7 @@
         <v>1903</v>
       </c>
       <c r="C105" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D105" t="s">
         <v>746</v>
@@ -17409,19 +17445,19 @@
         <v>748</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
         <v>624</v>
       </c>
@@ -17429,7 +17465,7 @@
         <v>1905</v>
       </c>
       <c r="C106" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D106" t="s">
         <v>746</v>
@@ -17441,16 +17477,16 @@
         <v>748</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
         <v>625</v>
       </c>
@@ -17458,7 +17494,7 @@
         <v>1906</v>
       </c>
       <c r="C107" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D107" t="s">
         <v>361</v>
@@ -17470,16 +17506,16 @@
         <v>748</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
         <v>626</v>
       </c>
@@ -17487,7 +17523,7 @@
         <v>1907</v>
       </c>
       <c r="C108" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D108" t="s">
         <v>746</v>
@@ -17499,13 +17535,13 @@
         <v>759</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>1472</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
         <v>623</v>
       </c>
@@ -17513,7 +17549,7 @@
         <v>1904</v>
       </c>
       <c r="C109" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F109" t="s">
         <v>748</v>
@@ -17521,7 +17557,7 @@
       <c r="G109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
         <v>627</v>
       </c>
@@ -17541,13 +17577,13 @@
         <v>748</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
         <v>628</v>
       </c>
@@ -17555,7 +17591,7 @@
         <v>2002</v>
       </c>
       <c r="C111" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D111" t="s">
         <v>746</v>
@@ -17567,13 +17603,13 @@
         <v>748</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A112" s="1" t="s">
         <v>629</v>
       </c>
@@ -17581,7 +17617,7 @@
         <v>2003</v>
       </c>
       <c r="C112" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D112" t="s">
         <v>746</v>
@@ -17593,16 +17629,16 @@
         <v>748</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
         <v>630</v>
       </c>
@@ -17610,7 +17646,7 @@
         <v>2004</v>
       </c>
       <c r="C113" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D113" t="s">
         <v>801</v>
@@ -17625,13 +17661,13 @@
         <v>492</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O113" s="1" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
         <v>631</v>
       </c>
@@ -17657,7 +17693,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
         <v>632</v>
       </c>
@@ -17665,7 +17701,7 @@
         <v>2006</v>
       </c>
       <c r="C115" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D115" t="s">
         <v>801</v>
@@ -17677,25 +17713,25 @@
         <v>759</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="1" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" s="12" customFormat="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A116" s="13" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B116" s="12">
         <v>2107</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>751</v>
@@ -17713,7 +17749,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="117" spans="1:15" s="12" customFormat="1">
+    <row r="117" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="13" t="s">
         <v>635</v>
       </c>
@@ -17721,7 +17757,7 @@
         <v>2103</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>746</v>
@@ -17733,16 +17769,16 @@
         <v>748</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="O117" s="13" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" s="12" customFormat="1">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A118" s="13" t="s">
         <v>638</v>
       </c>
@@ -17750,7 +17786,7 @@
         <v>2106</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>751</v>
@@ -17762,13 +17798,13 @@
         <v>748</v>
       </c>
       <c r="G118" s="13" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="O118" s="13" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" s="12" customFormat="1">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A119" s="13" t="s">
         <v>636</v>
       </c>
@@ -17776,7 +17812,7 @@
         <v>2104</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>746</v>
@@ -17788,14 +17824,14 @@
         <v>748</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="N119" s="13"/>
       <c r="O119" s="13" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" s="12" customFormat="1">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A120" s="13" t="s">
         <v>633</v>
       </c>
@@ -17803,7 +17839,7 @@
         <v>2101</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>773</v>
@@ -17815,16 +17851,16 @@
         <v>748</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="N120" s="13" t="s">
         <v>484</v>
       </c>
       <c r="O120" s="13" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" s="12" customFormat="1">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A121" s="13" t="s">
         <v>634</v>
       </c>
@@ -17832,7 +17868,7 @@
         <v>2102</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>746</v>
@@ -17844,16 +17880,16 @@
         <v>759</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H121" s="12" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="O121" s="13" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" s="12" customFormat="1">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A122" s="13" t="s">
         <v>637</v>
       </c>
@@ -17861,7 +17897,7 @@
         <v>2105</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>746</v>
@@ -17873,13 +17909,13 @@
         <v>766</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="O122" s="13" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A123" s="1" t="s">
         <v>642</v>
       </c>
@@ -17887,7 +17923,7 @@
         <v>2204</v>
       </c>
       <c r="C123" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D123" t="s">
         <v>751</v>
@@ -17899,14 +17935,14 @@
         <v>748</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>643</v>
       </c>
@@ -17914,7 +17950,7 @@
         <v>2205</v>
       </c>
       <c r="C124" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D124" t="s">
         <v>773</v>
@@ -17926,16 +17962,16 @@
         <v>748</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N124" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
         <v>644</v>
       </c>
@@ -17943,7 +17979,7 @@
         <v>2206</v>
       </c>
       <c r="C125" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D125" t="s">
         <v>746</v>
@@ -17955,23 +17991,23 @@
         <v>748</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="I125" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="J125" s="1" t="s">
         <v>1503</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>1504</v>
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
         <v>645</v>
       </c>
@@ -17979,7 +18015,7 @@
         <v>2207</v>
       </c>
       <c r="C126" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D126" t="s">
         <v>773</v>
@@ -17991,19 +18027,19 @@
         <v>748</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="N126" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>639</v>
       </c>
@@ -18011,7 +18047,7 @@
         <v>2201</v>
       </c>
       <c r="C127" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D127" t="s">
         <v>366</v>
@@ -18026,13 +18062,13 @@
         <v>494</v>
       </c>
       <c r="N127" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
         <v>640</v>
       </c>
@@ -18040,7 +18076,7 @@
         <v>2202</v>
       </c>
       <c r="C128" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D128" t="s">
         <v>746</v>
@@ -18052,16 +18088,16 @@
         <v>748</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N128" s="1" t="s">
         <v>485</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A129" s="1" t="s">
         <v>646</v>
       </c>
@@ -18069,7 +18105,7 @@
         <v>2208</v>
       </c>
       <c r="C129" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D129" t="s">
         <v>801</v>
@@ -18081,26 +18117,26 @@
         <v>748</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H129" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I129" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="J129" s="1" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
         <v>641</v>
       </c>
@@ -18108,7 +18144,7 @@
         <v>2203</v>
       </c>
       <c r="C130" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D130" t="s">
         <v>801</v>
@@ -18120,13 +18156,13 @@
         <v>766</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
         <v>649</v>
       </c>
@@ -18134,7 +18170,7 @@
         <v>2303</v>
       </c>
       <c r="C131" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D131" t="s">
         <v>801</v>
@@ -18146,22 +18182,22 @@
         <v>748</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="I131" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J131" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="J131" s="1" t="s">
-        <v>1509</v>
-      </c>
       <c r="O131" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
         <v>651</v>
       </c>
@@ -18169,7 +18205,7 @@
         <v>2306</v>
       </c>
       <c r="C132" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D132" t="s">
         <v>751</v>
@@ -18181,14 +18217,14 @@
         <v>748</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N132" s="1"/>
       <c r="O132" s="1" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>650</v>
       </c>
@@ -18196,7 +18232,7 @@
         <v>2304</v>
       </c>
       <c r="C133" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D133" t="s">
         <v>366</v>
@@ -18211,13 +18247,13 @@
         <v>495</v>
       </c>
       <c r="N133" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>647</v>
       </c>
@@ -18225,7 +18261,7 @@
         <v>2301</v>
       </c>
       <c r="C134" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D134" t="s">
         <v>773</v>
@@ -18237,25 +18273,25 @@
         <v>748</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H134" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="I134" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="I134" s="1" t="s">
+      <c r="J134" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>1507</v>
-      </c>
       <c r="N134" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>648</v>
       </c>
@@ -18263,7 +18299,7 @@
         <v>2302</v>
       </c>
       <c r="C135" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D135" t="s">
         <v>773</v>
@@ -18281,10 +18317,10 @@
         <v>486</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>652</v>
       </c>
@@ -18292,7 +18328,7 @@
         <v>2351</v>
       </c>
       <c r="C136" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D136" t="s">
         <v>773</v>
@@ -18304,16 +18340,16 @@
         <v>766</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="N136" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" s="12" customFormat="1">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A137" s="13" t="s">
         <v>653</v>
       </c>
@@ -18321,7 +18357,7 @@
         <v>2401</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D137" s="12" t="s">
         <v>751</v>
@@ -18333,13 +18369,13 @@
         <v>748</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="O137" s="13" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" s="12" customFormat="1">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A138" s="13" t="s">
         <v>654</v>
       </c>
@@ -18347,7 +18383,7 @@
         <v>2402</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D138" s="12" t="s">
         <v>773</v>
@@ -18359,22 +18395,22 @@
         <v>748</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="N138" s="12" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="O138" s="13" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" s="12" customFormat="1">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A139" s="13" t="s">
         <v>655</v>
       </c>
@@ -18382,7 +18418,7 @@
         <v>2403</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D139" s="12" t="s">
         <v>746</v>
@@ -18394,17 +18430,17 @@
         <v>748</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="N139" s="13"/>
       <c r="O139" s="13" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" s="12" customFormat="1">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="13" t="s">
         <v>656</v>
       </c>
@@ -18412,7 +18448,7 @@
         <v>2404</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D140" s="12" t="s">
         <v>746</v>
@@ -18424,17 +18460,17 @@
         <v>748</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="N140" s="13"/>
       <c r="O140" s="13" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" s="12" customFormat="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="13" t="s">
         <v>657</v>
       </c>
@@ -18442,7 +18478,7 @@
         <v>2405</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D141" s="12" t="s">
         <v>746</v>
@@ -18454,16 +18490,16 @@
         <v>748</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="O141" s="13" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" s="12" customFormat="1">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="13" t="s">
         <v>658</v>
       </c>
@@ -18471,7 +18507,7 @@
         <v>2406</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D142" s="12" t="s">
         <v>746</v>
@@ -18483,17 +18519,17 @@
         <v>748</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="N142" s="13"/>
       <c r="O142" s="13" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" s="12" customFormat="1">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="13" t="s">
         <v>659</v>
       </c>
@@ -18501,7 +18537,7 @@
         <v>2407</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D143" s="12" t="s">
         <v>773</v>
@@ -18513,16 +18549,16 @@
         <v>766</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="N143" s="12" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="O143" s="13" t="s">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" s="12" customFormat="1">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="13" t="s">
         <v>660</v>
       </c>
@@ -18530,7 +18566,7 @@
         <v>2408</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D144" s="12" t="s">
         <v>773</v>
@@ -18545,22 +18581,22 @@
         <v>503</v>
       </c>
       <c r="H144" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="I144" s="12" t="s">
         <v>1518</v>
       </c>
-      <c r="I144" s="12" t="s">
-        <v>1519</v>
-      </c>
       <c r="J144" s="12" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="N144" s="12" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="O144" s="13" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A145" s="1" t="s">
         <v>661</v>
       </c>
@@ -18568,7 +18604,7 @@
         <v>2501</v>
       </c>
       <c r="C145" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D145" t="s">
         <v>746</v>
@@ -18580,13 +18616,13 @@
         <v>748</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A146" s="1" t="s">
         <v>662</v>
       </c>
@@ -18594,7 +18630,7 @@
         <v>2502</v>
       </c>
       <c r="C146" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D146" t="s">
         <v>773</v>
@@ -18606,16 +18642,16 @@
         <v>748</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="N146" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A147" s="1" t="s">
         <v>663</v>
       </c>
@@ -18623,7 +18659,7 @@
         <v>2503</v>
       </c>
       <c r="C147" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D147" t="s">
         <v>751</v>
@@ -18635,14 +18671,14 @@
         <v>748</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A148" s="1" t="s">
         <v>664</v>
       </c>
@@ -18650,7 +18686,7 @@
         <v>2504</v>
       </c>
       <c r="C148" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D148" t="s">
         <v>751</v>
@@ -18665,28 +18701,28 @@
         <v>504</v>
       </c>
       <c r="H148" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="J148" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="I148" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>1577</v>
-      </c>
       <c r="K148" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L148" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="L148" s="1" t="s">
+      <c r="M148" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="M148" s="1" t="s">
-        <v>1531</v>
-      </c>
       <c r="O148" s="1" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A149" s="1" t="s">
         <v>665</v>
       </c>
@@ -18694,7 +18730,7 @@
         <v>2505</v>
       </c>
       <c r="C149" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D149" t="s">
         <v>746</v>
@@ -18706,19 +18742,19 @@
         <v>759</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A150" s="1" t="s">
         <v>666</v>
       </c>
@@ -18726,7 +18762,7 @@
         <v>2601</v>
       </c>
       <c r="C150" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D150" t="s">
         <v>746</v>
@@ -18738,22 +18774,22 @@
         <v>748</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A151" s="1" t="s">
         <v>667</v>
       </c>
@@ -18761,7 +18797,7 @@
         <v>2602</v>
       </c>
       <c r="C151" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D151" t="s">
         <v>773</v>
@@ -18776,16 +18812,16 @@
         <v>496</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N151" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A152" s="1" t="s">
         <v>668</v>
       </c>
@@ -18793,7 +18829,7 @@
         <v>2603</v>
       </c>
       <c r="C152" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D152" t="s">
         <v>746</v>
@@ -18808,13 +18844,13 @@
         <v>497</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A153" s="1" t="s">
         <v>669</v>
       </c>
@@ -18822,7 +18858,7 @@
         <v>2604</v>
       </c>
       <c r="C153" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D153" t="s">
         <v>801</v>
@@ -18834,25 +18870,25 @@
         <v>759</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A154" s="1" t="s">
         <v>670</v>
       </c>
@@ -18860,7 +18896,7 @@
         <v>2605</v>
       </c>
       <c r="C154" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D154" t="s">
         <v>801</v>
@@ -18872,33 +18908,33 @@
         <v>748</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="7" t="s">
         <v>1055</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>1548</v>
-      </c>
-      <c r="K154" s="1" t="s">
-        <v>1549</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" s="8" customFormat="1">
-      <c r="A155" s="7" t="s">
-        <v>1056</v>
       </c>
       <c r="B155" s="8">
         <v>2707</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>751</v>
@@ -18910,21 +18946,21 @@
         <v>748</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" s="8" customFormat="1">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="7" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B156" s="8">
         <v>2704</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>746</v>
@@ -18936,16 +18972,16 @@
         <v>748</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="O156" s="7" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" s="10" customFormat="1">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="9" t="s">
         <v>671</v>
       </c>
@@ -18953,7 +18989,7 @@
         <v>2703</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>746</v>
@@ -18965,30 +19001,30 @@
         <v>748</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="I157" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J157" s="10" t="s">
         <v>1520</v>
       </c>
-      <c r="J157" s="10" t="s">
-        <v>1521</v>
-      </c>
       <c r="O157" s="9" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" s="10" customFormat="1">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B158" s="10">
         <v>2701</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>746</v>
@@ -19000,22 +19036,22 @@
         <v>748</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H158" s="10" t="s">
+        <v>1581</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>1582</v>
+      </c>
+      <c r="J158" s="10" t="s">
         <v>1583</v>
       </c>
-      <c r="I158" s="10" t="s">
-        <v>1584</v>
-      </c>
-      <c r="J158" s="10" t="s">
-        <v>1585</v>
-      </c>
       <c r="O158" s="9" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" s="8" customFormat="1">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="7" t="s">
         <v>672</v>
       </c>
@@ -19023,7 +19059,7 @@
         <v>2705</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>801</v>
@@ -19035,16 +19071,16 @@
         <v>766</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="O159" s="7" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" s="8" customFormat="1">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="7" t="s">
         <v>673</v>
       </c>
@@ -19052,7 +19088,7 @@
         <v>2706</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>746</v>
@@ -19064,18 +19100,18 @@
         <v>759</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="O160" s="7" t="s">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A161" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B161">
         <v>2801</v>
@@ -19093,13 +19129,13 @@
         <v>748</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A162" s="1" t="s">
         <v>674</v>
       </c>
@@ -19119,14 +19155,14 @@
         <v>748</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N162" s="1"/>
       <c r="O162" s="1" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A163" s="1" t="s">
         <v>675</v>
       </c>
@@ -19134,7 +19170,7 @@
         <v>2803</v>
       </c>
       <c r="C163" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D163" t="s">
         <v>801</v>
@@ -19146,19 +19182,19 @@
         <v>748</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A164" s="1" t="s">
         <v>676</v>
       </c>
@@ -19166,7 +19202,7 @@
         <v>2806</v>
       </c>
       <c r="C164" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D164" t="s">
         <v>746</v>
@@ -19178,13 +19214,13 @@
         <v>748</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A165" s="1" t="s">
         <v>677</v>
       </c>
@@ -19192,7 +19228,7 @@
         <v>2807</v>
       </c>
       <c r="C165" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D165" t="s">
         <v>751</v>
@@ -19204,13 +19240,13 @@
         <v>748</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A166" s="1" t="s">
         <v>678</v>
       </c>
@@ -19218,7 +19254,7 @@
         <v>2808</v>
       </c>
       <c r="C166" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D166" t="s">
         <v>746</v>
@@ -19230,14 +19266,14 @@
         <v>759</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="N166" s="1"/>
       <c r="O166" s="1" t="s">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A167" s="1" t="s">
         <v>679</v>
       </c>
@@ -19245,7 +19281,7 @@
         <v>2809</v>
       </c>
       <c r="C167" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D167" t="s">
         <v>773</v>
@@ -19257,16 +19293,16 @@
         <v>748</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N167" t="s">
         <v>268</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A168" s="1" t="s">
         <v>680</v>
       </c>
@@ -19274,7 +19310,7 @@
         <v>2901</v>
       </c>
       <c r="C168" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D168" t="s">
         <v>801</v>
@@ -19286,14 +19322,14 @@
         <v>748</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="N168" s="1"/>
       <c r="O168" s="1" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A169" s="1" t="s">
         <v>681</v>
       </c>
@@ -19301,7 +19337,7 @@
         <v>2902</v>
       </c>
       <c r="C169" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D169" t="s">
         <v>801</v>
@@ -19313,25 +19349,25 @@
         <v>748</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="N169" s="1"/>
       <c r="O169" s="1" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A170" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B170">
         <v>2903</v>
       </c>
       <c r="C170" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D170" t="s">
         <v>751</v>
@@ -19343,13 +19379,13 @@
         <v>748</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A171" s="1" t="s">
         <v>682</v>
       </c>
@@ -19357,7 +19393,7 @@
         <v>2904</v>
       </c>
       <c r="C171" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D171" t="s">
         <v>746</v>
@@ -19369,16 +19405,16 @@
         <v>748</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A172" s="1" t="s">
         <v>683</v>
       </c>
@@ -19386,7 +19422,7 @@
         <v>2905</v>
       </c>
       <c r="C172" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D172" t="s">
         <v>773</v>
@@ -19398,19 +19434,19 @@
         <v>748</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="N172" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A173" s="1" t="s">
         <v>684</v>
       </c>
@@ -19418,7 +19454,7 @@
         <v>2906</v>
       </c>
       <c r="C173" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D173" t="s">
         <v>746</v>
@@ -19430,17 +19466,17 @@
         <v>759</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="N173" s="1"/>
       <c r="O173" s="1" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" s="12" customFormat="1">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A174" s="15" t="s">
         <v>685</v>
       </c>
@@ -19448,7 +19484,7 @@
         <v>3001</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D174" s="12" t="s">
         <v>773</v>
@@ -19460,16 +19496,16 @@
         <v>748</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="N174" s="12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O174" s="15" t="s">
         <v>1092</v>
       </c>
-      <c r="O174" s="15" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" s="12" customFormat="1">
+    </row>
+    <row r="175" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A175" s="15" t="s">
         <v>686</v>
       </c>
@@ -19477,7 +19513,7 @@
         <v>3002</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D175" s="12" t="s">
         <v>773</v>
@@ -19489,16 +19525,16 @@
         <v>748</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N175" s="12" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O175" s="15" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" s="12" customFormat="1">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A176" s="15" t="s">
         <v>687</v>
       </c>
@@ -19506,7 +19542,7 @@
         <v>3003</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D176" s="12" t="s">
         <v>801</v>
@@ -19518,23 +19554,23 @@
         <v>748</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H176" s="12" t="s">
+        <v>1511</v>
+      </c>
+      <c r="I176" s="12" t="s">
         <v>1512</v>
       </c>
-      <c r="I176" s="12" t="s">
+      <c r="J176" s="12" t="s">
         <v>1513</v>
-      </c>
-      <c r="J176" s="12" t="s">
-        <v>1514</v>
       </c>
       <c r="N176" s="15"/>
       <c r="O176" s="15" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" s="12" customFormat="1">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A177" s="15" t="s">
         <v>688</v>
       </c>
@@ -19542,7 +19578,7 @@
         <v>3004</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D177" s="12" t="s">
         <v>361</v>
@@ -19554,16 +19590,16 @@
         <v>748</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H177" s="12" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="O177" s="15" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" s="12" customFormat="1">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A178" s="15" t="s">
         <v>689</v>
       </c>
@@ -19571,7 +19607,7 @@
         <v>3005</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D178" s="12" t="s">
         <v>751</v>
@@ -19586,10 +19622,10 @@
         <v>498</v>
       </c>
       <c r="O178" s="15" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" s="12" customFormat="1">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A179" s="15" t="s">
         <v>690</v>
       </c>
@@ -19597,7 +19633,7 @@
         <v>3006</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>773</v>
@@ -19609,16 +19645,16 @@
         <v>759</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="N179" s="12" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="O179" s="15" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" s="12" customFormat="1">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A180" s="15" t="s">
         <v>691</v>
       </c>
@@ -19626,7 +19662,7 @@
         <v>3007</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>746</v>
@@ -19638,16 +19674,16 @@
         <v>759</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H180" s="12" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="O180" s="15" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" s="8" customFormat="1">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A181" s="14" t="s">
         <v>692</v>
       </c>
@@ -19655,7 +19691,7 @@
         <v>3101</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>746</v>
@@ -19667,16 +19703,16 @@
         <v>748</v>
       </c>
       <c r="G181" s="14" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O181" s="14" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" s="8" customFormat="1">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A182" s="14" t="s">
         <v>693</v>
       </c>
@@ -19684,7 +19720,7 @@
         <v>3102</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D182" s="8" t="s">
         <v>773</v>
@@ -19699,13 +19735,13 @@
         <v>505</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I182" s="8" t="s">
+        <v>1531</v>
+      </c>
+      <c r="J182" s="8" t="s">
         <v>1532</v>
-      </c>
-      <c r="J182" s="8" t="s">
-        <v>1533</v>
       </c>
       <c r="N182" s="8" t="s">
         <v>269</v>
@@ -19714,7 +19750,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="183" spans="1:15" s="8" customFormat="1">
+    <row r="183" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A183" s="14" t="s">
         <v>694</v>
       </c>
@@ -19722,7 +19758,7 @@
         <v>3103</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>751</v>
@@ -19741,7 +19777,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="184" spans="1:15" s="8" customFormat="1">
+    <row r="184" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A184" s="14" t="s">
         <v>695</v>
       </c>
@@ -19749,7 +19785,7 @@
         <v>3105</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D184" s="8" t="s">
         <v>746</v>
@@ -19764,22 +19800,22 @@
         <v>507</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I184" s="8" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="J184" s="8" t="s">
+        <v>1522</v>
+      </c>
+      <c r="K184" s="8" t="s">
         <v>1523</v>
-      </c>
-      <c r="K184" s="8" t="s">
-        <v>1524</v>
       </c>
       <c r="O184" s="14" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="185" spans="1:15" s="8" customFormat="1">
+    <row r="185" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A185" s="14" t="s">
         <v>696</v>
       </c>
@@ -19787,7 +19823,7 @@
         <v>3106</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>746</v>
@@ -19802,25 +19838,25 @@
         <v>508</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="I185" s="8" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J185" s="8" t="s">
         <v>1525</v>
       </c>
-      <c r="J185" s="8" t="s">
+      <c r="K185" s="8" t="s">
         <v>1526</v>
       </c>
-      <c r="K185" s="8" t="s">
+      <c r="L185" s="8" t="s">
         <v>1527</v>
-      </c>
-      <c r="L185" s="8" t="s">
-        <v>1528</v>
       </c>
       <c r="O185" s="14" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="186" spans="1:15" s="8" customFormat="1">
+    <row r="186" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A186" s="14" t="s">
         <v>697</v>
       </c>
@@ -19828,7 +19864,7 @@
         <v>3107</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D186" s="8" t="s">
         <v>801</v>
@@ -19843,13 +19879,13 @@
         <v>509</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="O186" s="14" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="187" spans="1:15">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A187" s="1" t="s">
         <v>698</v>
       </c>
@@ -19857,10 +19893,10 @@
         <v>3201</v>
       </c>
       <c r="C187" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D187" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E187" t="s">
         <v>747</v>
@@ -19870,11 +19906,11 @@
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A188" s="1" t="s">
         <v>699</v>
       </c>
@@ -19882,10 +19918,10 @@
         <v>3202</v>
       </c>
       <c r="C188" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D188" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E188" t="s">
         <v>747</v>
@@ -19895,16 +19931,16 @@
       </c>
       <c r="G188" s="1"/>
       <c r="H188" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:15">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A189" s="1" t="s">
         <v>700</v>
       </c>
@@ -19912,7 +19948,7 @@
         <v>3203</v>
       </c>
       <c r="C189" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D189" t="s">
         <v>746</v>
@@ -19925,13 +19961,13 @@
       </c>
       <c r="G189" s="1"/>
       <c r="H189" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="O189" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A190" s="1" t="s">
         <v>701</v>
       </c>
@@ -19939,10 +19975,10 @@
         <v>3301</v>
       </c>
       <c r="C190" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D190" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E190" t="s">
         <v>747</v>
@@ -19952,11 +19988,11 @@
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A191" s="1" t="s">
         <v>702</v>
       </c>
@@ -19964,10 +20000,10 @@
         <v>3302</v>
       </c>
       <c r="C191" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D191" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E191" t="s">
         <v>747</v>
@@ -19977,11 +20013,11 @@
       </c>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A192" s="1" t="s">
         <v>703</v>
       </c>
@@ -19989,10 +20025,10 @@
         <v>3303</v>
       </c>
       <c r="C192" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D192" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E192" t="s">
         <v>747</v>
@@ -20003,7 +20039,7 @@
       <c r="G192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A193" s="1" t="s">
         <v>704</v>
       </c>
@@ -20011,10 +20047,10 @@
         <v>3304</v>
       </c>
       <c r="C193" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D193" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E193" t="s">
         <v>747</v>
@@ -20025,7 +20061,7 @@
       <c r="G193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A194" s="1" t="s">
         <v>705</v>
       </c>
@@ -20033,10 +20069,10 @@
         <v>3306</v>
       </c>
       <c r="C194" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D194" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E194" t="s">
         <v>747</v>
@@ -20046,11 +20082,11 @@
       </c>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A195" s="1" t="s">
         <v>706</v>
       </c>
@@ -20058,10 +20094,10 @@
         <v>3401</v>
       </c>
       <c r="C195" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D195" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E195" t="s">
         <v>747</v>
@@ -20074,7 +20110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A196" s="1" t="s">
         <v>707</v>
       </c>
@@ -20082,10 +20118,10 @@
         <v>3402</v>
       </c>
       <c r="C196" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D196" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E196" t="s">
         <v>747</v>
@@ -20098,7 +20134,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A197" s="1" t="s">
         <v>708</v>
       </c>
@@ -20106,10 +20142,10 @@
         <v>3403</v>
       </c>
       <c r="C197" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D197" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E197" t="s">
         <v>747</v>
@@ -20122,7 +20158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A198" s="1" t="s">
         <v>709</v>
       </c>
@@ -20130,10 +20166,10 @@
         <v>3404</v>
       </c>
       <c r="C198" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D198" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E198" t="s">
         <v>747</v>
@@ -20143,13 +20179,13 @@
       </c>
       <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="O198" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A199" s="1" t="s">
         <v>710</v>
       </c>
@@ -20157,10 +20193,10 @@
         <v>3405</v>
       </c>
       <c r="C199" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D199" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E199" t="s">
         <v>747</v>
@@ -20170,11 +20206,11 @@
       </c>
       <c r="G199" s="1"/>
       <c r="H199" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A200" s="1" t="s">
         <v>711</v>
       </c>
@@ -20182,10 +20218,10 @@
         <v>3501</v>
       </c>
       <c r="C200" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D200" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E200" t="s">
         <v>747</v>
@@ -20196,7 +20232,7 @@
       <c r="G200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A201" s="1" t="s">
         <v>712</v>
       </c>
@@ -20204,10 +20240,10 @@
         <v>3502</v>
       </c>
       <c r="C201" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D201" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E201" t="s">
         <v>747</v>
@@ -20220,7 +20256,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
         <v>713</v>
       </c>
@@ -20228,10 +20264,10 @@
         <v>3503</v>
       </c>
       <c r="C202" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D202" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E202" t="s">
         <v>747</v>
@@ -20241,13 +20277,13 @@
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="O202" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:15">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A203" s="1" t="s">
         <v>714</v>
       </c>
@@ -20255,10 +20291,10 @@
         <v>3504</v>
       </c>
       <c r="C203" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D203" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E203" t="s">
         <v>747</v>
@@ -20268,11 +20304,11 @@
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A204" s="1" t="s">
         <v>715</v>
       </c>
@@ -20280,7 +20316,7 @@
         <v>3505</v>
       </c>
       <c r="C204" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D204" t="s">
         <v>746</v>
@@ -20293,13 +20329,13 @@
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="O204" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A205" s="1" t="s">
         <v>716</v>
       </c>
@@ -20307,10 +20343,10 @@
         <v>3506</v>
       </c>
       <c r="C205" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D205" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="E205" t="s">
         <v>747</v>
@@ -20320,13 +20356,13 @@
       </c>
       <c r="G205" s="1"/>
       <c r="H205" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="O205" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A206" s="1" t="s">
         <v>717</v>
       </c>
@@ -20334,10 +20370,10 @@
         <v>3507</v>
       </c>
       <c r="C206" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D206" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E206" t="s">
         <v>747</v>
@@ -20350,7 +20386,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A207" s="1" t="s">
         <v>718</v>
       </c>
@@ -20358,10 +20394,10 @@
         <v>3601</v>
       </c>
       <c r="C207" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D207" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="E207" t="s">
         <v>747</v>
@@ -20374,7 +20410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A208" s="1" t="s">
         <v>719</v>
       </c>
@@ -20382,10 +20418,10 @@
         <v>3602</v>
       </c>
       <c r="C208" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D208" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E208" t="s">
         <v>747</v>
@@ -20398,7 +20434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A209" s="1" t="s">
         <v>720</v>
       </c>
@@ -20406,10 +20442,10 @@
         <v>3603</v>
       </c>
       <c r="C209" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D209" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E209" t="s">
         <v>747</v>
@@ -20420,7 +20456,7 @@
       <c r="G209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A210" s="1" t="s">
         <v>721</v>
       </c>
@@ -20428,10 +20464,10 @@
         <v>3604</v>
       </c>
       <c r="C210" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D210" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E210" t="s">
         <v>747</v>
@@ -20441,16 +20477,16 @@
       </c>
       <c r="G210" s="1"/>
       <c r="H210" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="O210" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A211" s="1" t="s">
         <v>722</v>
       </c>
@@ -20458,10 +20494,10 @@
         <v>3605</v>
       </c>
       <c r="C211" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D211" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E211" t="s">
         <v>747</v>
@@ -20471,13 +20507,13 @@
       </c>
       <c r="G211" s="1"/>
       <c r="H211" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="O211" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A212" s="1" t="s">
         <v>723</v>
       </c>
@@ -20485,7 +20521,7 @@
         <v>3606</v>
       </c>
       <c r="C212" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D212" t="s">
         <v>746</v>
@@ -20498,13 +20534,13 @@
       </c>
       <c r="G212" s="1"/>
       <c r="H212" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A213" s="1" t="s">
         <v>724</v>
       </c>
@@ -20512,10 +20548,10 @@
         <v>3607</v>
       </c>
       <c r="C213" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D213" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E213" t="s">
         <v>747</v>
@@ -20525,11 +20561,11 @@
       </c>
       <c r="G213" s="1"/>
       <c r="H213" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A214" s="1" t="s">
         <v>725</v>
       </c>
@@ -20537,7 +20573,7 @@
         <v>3701</v>
       </c>
       <c r="C214" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D214" t="s">
         <v>751</v>
@@ -20551,7 +20587,7 @@
       <c r="G214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A215" s="1" t="s">
         <v>726</v>
       </c>
@@ -20559,7 +20595,7 @@
         <v>3702</v>
       </c>
       <c r="C215" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D215" t="s">
         <v>773</v>
@@ -20572,14 +20608,14 @@
       </c>
       <c r="G215" s="1"/>
       <c r="H215" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A216" s="1" t="s">
         <v>727</v>
       </c>
@@ -20587,7 +20623,7 @@
         <v>3703</v>
       </c>
       <c r="C216" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D216" t="s">
         <v>773</v>
@@ -20596,12 +20632,12 @@
         <v>754</v>
       </c>
       <c r="F216" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A217" s="1" t="s">
         <v>728</v>
       </c>
@@ -20609,7 +20645,7 @@
         <v>3704</v>
       </c>
       <c r="C217" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D217" t="s">
         <v>773</v>
@@ -20618,12 +20654,12 @@
         <v>754</v>
       </c>
       <c r="F217" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A218" s="1" t="s">
         <v>729</v>
       </c>
@@ -20631,7 +20667,7 @@
         <v>3705</v>
       </c>
       <c r="C218" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D218" t="s">
         <v>746</v>
@@ -20645,7 +20681,7 @@
       <c r="G218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A219" s="1" t="s">
         <v>730</v>
       </c>
@@ -20653,7 +20689,7 @@
         <v>3706</v>
       </c>
       <c r="C219" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D219" t="s">
         <v>773</v>
@@ -20662,15 +20698,15 @@
         <v>792</v>
       </c>
       <c r="F219" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G219" s="1"/>
       <c r="H219" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A220" s="1" t="s">
         <v>731</v>
       </c>
@@ -20678,7 +20714,7 @@
         <v>3707</v>
       </c>
       <c r="C220" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D220" t="s">
         <v>801</v>
@@ -20691,11 +20727,11 @@
       </c>
       <c r="G220" s="1"/>
       <c r="H220" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A221" s="1" t="s">
         <v>732</v>
       </c>
@@ -20703,10 +20739,10 @@
         <v>32011</v>
       </c>
       <c r="C221" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D221" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E221" t="s">
         <v>747</v>
@@ -20716,11 +20752,11 @@
       </c>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A222" s="1" t="s">
         <v>733</v>
       </c>
@@ -20728,7 +20764,7 @@
         <v>32031</v>
       </c>
       <c r="C222" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D222" t="s">
         <v>746</v>
@@ -20744,7 +20780,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A223" s="1" t="s">
         <v>734</v>
       </c>
@@ -20752,10 +20788,10 @@
         <v>36021</v>
       </c>
       <c r="C223" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D223" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E223" t="s">
         <v>747</v>
@@ -20768,7 +20804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A224" s="1" t="s">
         <v>735</v>
       </c>
@@ -20776,10 +20812,10 @@
         <v>36051</v>
       </c>
       <c r="C224" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D224" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E224" t="s">
         <v>747</v>
@@ -20792,7 +20828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A225" s="1" t="s">
         <v>736</v>
       </c>
@@ -20800,7 +20836,7 @@
         <v>36061</v>
       </c>
       <c r="C225" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D225" t="s">
         <v>361</v>
@@ -20813,13 +20849,13 @@
       </c>
       <c r="G225" s="1"/>
       <c r="H225" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="O225" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A226" s="1" t="s">
         <v>737</v>
       </c>
@@ -20827,7 +20863,7 @@
         <v>36062</v>
       </c>
       <c r="C226" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D226" t="s">
         <v>746</v>
@@ -20840,13 +20876,13 @@
       </c>
       <c r="G226" s="1"/>
       <c r="H226" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="O226" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A227" s="1" t="s">
         <v>738</v>
       </c>
@@ -20854,10 +20890,10 @@
         <v>36071</v>
       </c>
       <c r="C227" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D227" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E227" t="s">
         <v>747</v>
@@ -20868,7 +20904,7 @@
       <c r="G227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>739</v>
       </c>
@@ -20876,7 +20912,7 @@
         <v>37021</v>
       </c>
       <c r="C228" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D228" t="s">
         <v>746</v>
@@ -20885,16 +20921,16 @@
         <v>754</v>
       </c>
       <c r="F228" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H228" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I228" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>740</v>
       </c>
@@ -20902,7 +20938,7 @@
         <v>37051</v>
       </c>
       <c r="C229" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D229" t="s">
         <v>746</v>
@@ -20911,13 +20947,13 @@
         <v>747</v>
       </c>
       <c r="F229" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H229" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>741</v>
       </c>
@@ -20925,7 +20961,7 @@
         <v>37052</v>
       </c>
       <c r="C230" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D230" t="s">
         <v>751</v>
@@ -20937,7 +20973,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>742</v>
       </c>
@@ -20945,13 +20981,13 @@
         <v>37071</v>
       </c>
       <c r="C231" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F231" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>743</v>
       </c>
@@ -20959,10 +20995,10 @@
         <v>360711</v>
       </c>
       <c r="C232" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D232" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E232" t="s">
         <v>747</v>
@@ -20971,7 +21007,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>744</v>
       </c>
@@ -20979,10 +21015,10 @@
         <v>360712</v>
       </c>
       <c r="C233" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D233" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E233" t="s">
         <v>747</v>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBE0100-9421-48D4-9923-1DB8472649C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4815" yWindow="952" windowWidth="14415" windowHeight="13171" tabRatio="631" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>
@@ -6017,7 +6017,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6440,7 +6440,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5839A4A7-E3EE-408B-ABC6-26D91AFB7BC6}">
   <dimension ref="A1:T42"/>
-  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.06640625" style="4"/>
@@ -6463,7 +6463,7 @@
     <col min="20" max="20" width="129.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1">
+    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>109</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1150</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>1151</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>1152</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>1153</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>1154</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>1155</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>1156</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>1157</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>1158</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>1159</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>1160</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>1161</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>1162</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>1163</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>1164</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>1165</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>1166</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>1167</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>1168</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>1169</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>1170</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>1171</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>1172</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>1173</v>
       </c>
@@ -7936,7 +7936,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>1174</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>1175</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>1176</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>1177</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>1178</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>1179</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>1180</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>1181</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>1182</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>1183</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>1184</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>1185</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>1186</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>1187</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>1188</v>
       </c>
@@ -8839,7 +8839,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7A31B9-DA13-42EA-9657-5BB3EA92E677}">
   <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="16.59765625" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
@@ -8853,7 +8853,7 @@
     <col min="11" max="11" width="255.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>109</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -9168,7 +9168,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>120</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>122</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>128</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>129</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>130</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>138</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>141</v>
       </c>
@@ -10043,7 +10043,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>143</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>144</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>145</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>148</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>149</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>154</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>155</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>156</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>164</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -10883,7 +10883,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>166</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>167</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>168</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>170</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>171</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>172</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>173</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>174</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>175</v>
       </c>
@@ -11233,7 +11233,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>176</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>177</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>178</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>179</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>180</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>181</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>182</v>
       </c>
@@ -11478,7 +11478,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>183</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>184</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>185</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>186</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>189</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>190</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>191</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>192</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>193</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>194</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>195</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -11968,7 +11968,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>199</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>200</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>202</v>
       </c>
@@ -12178,7 +12178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>206</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>207</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>208</v>
       </c>
@@ -12388,7 +12388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>211</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>212</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -12563,7 +12563,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>217</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>219</v>
       </c>
@@ -12773,7 +12773,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>220</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>221</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>222</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -12913,7 +12913,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>224</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>225</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>226</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>227</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>228</v>
       </c>
@@ -13088,7 +13088,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>229</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>230</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>231</v>
       </c>
@@ -13193,7 +13193,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>232</v>
       </c>
@@ -13228,7 +13228,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>233</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>234</v>
       </c>
@@ -13298,7 +13298,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>235</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>236</v>
       </c>
@@ -13368,7 +13368,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>237</v>
       </c>
@@ -13403,7 +13403,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>238</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>239</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>241</v>
       </c>
@@ -13543,7 +13543,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>242</v>
       </c>
@@ -13578,7 +13578,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>243</v>
       </c>
@@ -13613,7 +13613,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>245</v>
       </c>
@@ -13683,7 +13683,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>246</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>247</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>248</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>249</v>
       </c>
@@ -13823,7 +13823,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>250</v>
       </c>
@@ -13858,7 +13858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>251</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>252</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>254</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>255</v>
       </c>
@@ -14033,7 +14033,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>256</v>
       </c>
@@ -14068,7 +14068,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>257</v>
       </c>
@@ -14103,7 +14103,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>258</v>
       </c>
@@ -14138,7 +14138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>259</v>
       </c>
@@ -14173,7 +14173,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>260</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>261</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>262</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>263</v>
       </c>
@@ -14313,7 +14313,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>264</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>265</v>
       </c>
@@ -14392,7 +14392,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064C6D04-9B4F-44DE-8444-798F1E3ED691}">
   <dimension ref="A1:O233"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.86328125" customWidth="1"/>
     <col min="2" max="2" width="8.06640625" bestFit="1" customWidth="1"/>
@@ -14402,7 +14402,7 @@
     <col min="15" max="15" width="20.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -14449,7 +14449,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -14496,7 +14496,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -14543,7 +14543,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1462</v>
       </c>
@@ -14569,7 +14569,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>527</v>
       </c>
@@ -14601,7 +14601,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>526</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>525</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>528</v>
       </c>
@@ -14679,7 +14679,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>531</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>529</v>
       </c>
@@ -14731,7 +14731,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>530</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>532</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>536</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>537</v>
       </c>
@@ -14838,7 +14838,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>534</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>533</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>535</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>543</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>541</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>539</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>540</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>538</v>
       </c>
@@ -15046,7 +15046,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>542</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>544</v>
       </c>
@@ -15104,7 +15104,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>545</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>546</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>547</v>
       </c>
@@ -15191,7 +15191,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>548</v>
       </c>
@@ -15220,7 +15220,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>551</v>
       </c>
@@ -15253,7 +15253,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>549</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>550</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>552</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>553</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>556</v>
       </c>
@@ -15404,7 +15404,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>555</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>557</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>554</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>558</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>559</v>
       </c>
@@ -15556,7 +15556,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>560</v>
       </c>
@@ -15588,7 +15588,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>561</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>562</v>
       </c>
@@ -15643,7 +15643,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>563</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>564</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>565</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>566</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>567</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>568</v>
       </c>
@@ -15811,7 +15811,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>1466</v>
       </c>
@@ -15840,7 +15840,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>574</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>569</v>
       </c>
@@ -15899,7 +15899,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>570</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>575</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>572</v>
       </c>
@@ -15986,7 +15986,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>573</v>
       </c>
@@ -16018,7 +16018,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>571</v>
       </c>
@@ -16050,7 +16050,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>583</v>
       </c>
@@ -16076,7 +16076,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>581</v>
       </c>
@@ -16105,7 +16105,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>579</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>577</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>578</v>
       </c>
@@ -16183,7 +16183,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>576</v>
       </c>
@@ -16210,7 +16210,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>580</v>
       </c>
@@ -16237,7 +16237,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>582</v>
       </c>
@@ -16266,7 +16266,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>584</v>
       </c>
@@ -16295,7 +16295,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>879</v>
       </c>
@@ -16321,7 +16321,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>882</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>585</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>586</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>587</v>
       </c>
@@ -16437,7 +16437,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>588</v>
       </c>
@@ -16464,7 +16464,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>589</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>590</v>
       </c>
@@ -16520,7 +16520,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>591</v>
       </c>
@@ -16552,7 +16552,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>592</v>
       </c>
@@ -16581,7 +16581,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>901</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
         <v>593</v>
       </c>
@@ -16635,7 +16635,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>595</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
         <v>596</v>
       </c>
@@ -16691,7 +16691,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>594</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>597</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>598</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>599</v>
       </c>
@@ -16808,7 +16808,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>600</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>601</v>
       </c>
@@ -16866,7 +16866,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>602</v>
       </c>
@@ -16899,7 +16899,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>603</v>
       </c>
@@ -16931,7 +16931,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>607</v>
       </c>
@@ -16960,7 +16960,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>608</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>605</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>604</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>606</v>
       </c>
@@ -17077,7 +17077,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>609</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>610</v>
       </c>
@@ -17133,7 +17133,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>613</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>611</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>612</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="6" customFormat="1">
+    <row r="98" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
         <v>615</v>
       </c>
@@ -17250,7 +17250,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="99" spans="1:15" s="6" customFormat="1">
+    <row r="99" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
         <v>614</v>
       </c>
@@ -17279,7 +17279,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
         <v>616</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
         <v>617</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
         <v>618</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
         <v>619</v>
       </c>
@@ -17395,7 +17395,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
         <v>620</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
         <v>621</v>
       </c>
@@ -17453,7 +17453,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
         <v>623</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
         <v>624</v>
       </c>
@@ -17511,7 +17511,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
         <v>625</v>
       </c>
@@ -17537,7 +17537,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
         <v>622</v>
       </c>
@@ -17553,7 +17553,7 @@
       <c r="G109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
         <v>626</v>
       </c>
@@ -17579,7 +17579,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
         <v>627</v>
       </c>
@@ -17605,7 +17605,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A112" s="1" t="s">
         <v>628</v>
       </c>
@@ -17634,7 +17634,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
         <v>629</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
         <v>630</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
         <v>631</v>
       </c>
@@ -17719,7 +17719,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="116" spans="1:15" s="12" customFormat="1">
+    <row r="116" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A116" s="13" t="s">
         <v>972</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="117" spans="1:15" s="12" customFormat="1">
+    <row r="117" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="13" t="s">
         <v>634</v>
       </c>
@@ -17774,7 +17774,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="118" spans="1:15" s="12" customFormat="1">
+    <row r="118" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A118" s="13" t="s">
         <v>637</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="119" spans="1:15" s="12" customFormat="1">
+    <row r="119" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A119" s="13" t="s">
         <v>635</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="120" spans="1:15" s="12" customFormat="1">
+    <row r="120" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A120" s="13" t="s">
         <v>632</v>
       </c>
@@ -17856,7 +17856,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="121" spans="1:15" s="12" customFormat="1">
+    <row r="121" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A121" s="13" t="s">
         <v>633</v>
       </c>
@@ -17885,7 +17885,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="12" customFormat="1">
+    <row r="122" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A122" s="13" t="s">
         <v>636</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="123" spans="1:15">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A123" s="1" t="s">
         <v>641</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>642</v>
       </c>
@@ -17967,7 +17967,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
         <v>643</v>
       </c>
@@ -18003,7 +18003,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
         <v>644</v>
       </c>
@@ -18035,7 +18035,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>638</v>
       </c>
@@ -18064,7 +18064,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
         <v>639</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="129" spans="1:15">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A129" s="1" t="s">
         <v>645</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
         <v>640</v>
       </c>
@@ -18158,7 +18158,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="131" spans="1:15">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
         <v>648</v>
       </c>
@@ -18193,7 +18193,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="132" spans="1:15">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
         <v>650</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>649</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="134" spans="1:15">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>646</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="135" spans="1:15">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>647</v>
       </c>
@@ -18316,7 +18316,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>651</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="137" spans="1:15" s="12" customFormat="1">
+    <row r="137" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A137" s="13" t="s">
         <v>652</v>
       </c>
@@ -18371,7 +18371,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="12" customFormat="1">
+    <row r="138" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A138" s="13" t="s">
         <v>653</v>
       </c>
@@ -18406,7 +18406,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="139" spans="1:15" s="12" customFormat="1">
+    <row r="139" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A139" s="13" t="s">
         <v>654</v>
       </c>
@@ -18436,7 +18436,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="12" customFormat="1">
+    <row r="140" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="13" t="s">
         <v>655</v>
       </c>
@@ -18466,7 +18466,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="141" spans="1:15" s="12" customFormat="1">
+    <row r="141" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="13" t="s">
         <v>656</v>
       </c>
@@ -18495,7 +18495,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="142" spans="1:15" s="12" customFormat="1">
+    <row r="142" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="13" t="s">
         <v>657</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="143" spans="1:15" s="12" customFormat="1">
+    <row r="143" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="13" t="s">
         <v>658</v>
       </c>
@@ -18554,7 +18554,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="144" spans="1:15" s="12" customFormat="1">
+    <row r="144" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="13" t="s">
         <v>659</v>
       </c>
@@ -18592,7 +18592,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A145" s="1" t="s">
         <v>660</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A146" s="1" t="s">
         <v>661</v>
       </c>
@@ -18647,7 +18647,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A147" s="1" t="s">
         <v>662</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A148" s="1" t="s">
         <v>663</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A149" s="1" t="s">
         <v>664</v>
       </c>
@@ -18750,7 +18750,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A150" s="1" t="s">
         <v>665</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A151" s="1" t="s">
         <v>666</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A152" s="1" t="s">
         <v>667</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A153" s="1" t="s">
         <v>668</v>
       </c>
@@ -18884,7 +18884,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A154" s="1" t="s">
         <v>669</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="8" customFormat="1">
+    <row r="155" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="7" t="s">
         <v>1054</v>
       </c>
@@ -18948,7 +18948,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="156" spans="1:15" s="8" customFormat="1">
+    <row r="156" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="7" t="s">
         <v>1540</v>
       </c>
@@ -18977,7 +18977,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="157" spans="1:15" s="10" customFormat="1">
+    <row r="157" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="9" t="s">
         <v>670</v>
       </c>
@@ -19012,7 +19012,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="10" customFormat="1">
+    <row r="158" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9" t="s">
         <v>1542</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="8" customFormat="1">
+    <row r="159" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="7" t="s">
         <v>671</v>
       </c>
@@ -19076,7 +19076,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="8" customFormat="1">
+    <row r="160" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="7" t="s">
         <v>672</v>
       </c>
@@ -19105,7 +19105,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A161" s="1" t="s">
         <v>1467</v>
       </c>
@@ -19131,7 +19131,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A162" s="1" t="s">
         <v>673</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A163" s="1" t="s">
         <v>674</v>
       </c>
@@ -19190,7 +19190,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A164" s="1" t="s">
         <v>675</v>
       </c>
@@ -19216,7 +19216,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A165" s="1" t="s">
         <v>676</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A166" s="1" t="s">
         <v>677</v>
       </c>
@@ -19269,7 +19269,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A167" s="1" t="s">
         <v>678</v>
       </c>
@@ -19298,7 +19298,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A168" s="1" t="s">
         <v>679</v>
       </c>
@@ -19325,7 +19325,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A169" s="1" t="s">
         <v>680</v>
       </c>
@@ -19355,7 +19355,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A170" s="1" t="s">
         <v>1079</v>
       </c>
@@ -19381,7 +19381,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A171" s="1" t="s">
         <v>681</v>
       </c>
@@ -19410,7 +19410,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A172" s="1" t="s">
         <v>682</v>
       </c>
@@ -19442,7 +19442,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A173" s="1" t="s">
         <v>683</v>
       </c>
@@ -19472,7 +19472,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="174" spans="1:15" s="12" customFormat="1">
+    <row r="174" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A174" s="15" t="s">
         <v>684</v>
       </c>
@@ -19501,7 +19501,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="175" spans="1:15" s="12" customFormat="1">
+    <row r="175" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A175" s="15" t="s">
         <v>685</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="176" spans="1:15" s="12" customFormat="1">
+    <row r="176" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A176" s="15" t="s">
         <v>686</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="177" spans="1:15" s="12" customFormat="1">
+    <row r="177" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A177" s="15" t="s">
         <v>687</v>
       </c>
@@ -19595,7 +19595,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="178" spans="1:15" s="12" customFormat="1">
+    <row r="178" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A178" s="15" t="s">
         <v>688</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="179" spans="1:15" s="12" customFormat="1">
+    <row r="179" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A179" s="15" t="s">
         <v>689</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="180" spans="1:15" s="12" customFormat="1">
+    <row r="180" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A180" s="15" t="s">
         <v>690</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="181" spans="1:15" s="8" customFormat="1">
+    <row r="181" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A181" s="14" t="s">
         <v>691</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="182" spans="1:15" s="8" customFormat="1">
+    <row r="182" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A182" s="14" t="s">
         <v>692</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="183" spans="1:15" s="8" customFormat="1">
+    <row r="183" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A183" s="14" t="s">
         <v>693</v>
       </c>
@@ -19773,7 +19773,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="184" spans="1:15" s="8" customFormat="1">
+    <row r="184" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A184" s="14" t="s">
         <v>694</v>
       </c>
@@ -19811,7 +19811,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="185" spans="1:15" s="8" customFormat="1">
+    <row r="185" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A185" s="14" t="s">
         <v>695</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="186" spans="1:15" s="8" customFormat="1">
+    <row r="186" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A186" s="14" t="s">
         <v>696</v>
       </c>
@@ -19881,7 +19881,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="187" spans="1:15">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A187" s="1" t="s">
         <v>697</v>
       </c>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A188" s="1" t="s">
         <v>698</v>
       </c>
@@ -19936,7 +19936,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:15">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A189" s="1" t="s">
         <v>699</v>
       </c>
@@ -19963,7 +19963,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:15">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A190" s="1" t="s">
         <v>700</v>
       </c>
@@ -19988,7 +19988,7 @@
       </c>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A191" s="1" t="s">
         <v>701</v>
       </c>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A192" s="1" t="s">
         <v>702</v>
       </c>
@@ -20035,7 +20035,7 @@
       <c r="G192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A193" s="1" t="s">
         <v>703</v>
       </c>
@@ -20057,7 +20057,7 @@
       <c r="G193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A194" s="1" t="s">
         <v>704</v>
       </c>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A195" s="1" t="s">
         <v>705</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A196" s="1" t="s">
         <v>706</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A197" s="1" t="s">
         <v>707</v>
       </c>
@@ -20154,7 +20154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A198" s="1" t="s">
         <v>708</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A199" s="1" t="s">
         <v>709</v>
       </c>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A200" s="1" t="s">
         <v>710</v>
       </c>
@@ -20228,7 +20228,7 @@
       <c r="G200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A201" s="1" t="s">
         <v>711</v>
       </c>
@@ -20252,7 +20252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
         <v>712</v>
       </c>
@@ -20279,7 +20279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:15">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A203" s="1" t="s">
         <v>713</v>
       </c>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A204" s="1" t="s">
         <v>714</v>
       </c>
@@ -20331,7 +20331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:15">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A205" s="1" t="s">
         <v>715</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A206" s="1" t="s">
         <v>716</v>
       </c>
@@ -20382,7 +20382,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A207" s="1" t="s">
         <v>717</v>
       </c>
@@ -20406,7 +20406,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A208" s="1" t="s">
         <v>718</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A209" s="1" t="s">
         <v>719</v>
       </c>
@@ -20452,7 +20452,7 @@
       <c r="G209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A210" s="1" t="s">
         <v>720</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A211" s="1" t="s">
         <v>721</v>
       </c>
@@ -20509,7 +20509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A212" s="1" t="s">
         <v>722</v>
       </c>
@@ -20536,7 +20536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A213" s="1" t="s">
         <v>723</v>
       </c>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A214" s="1" t="s">
         <v>724</v>
       </c>
@@ -20583,7 +20583,7 @@
       <c r="G214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A215" s="1" t="s">
         <v>725</v>
       </c>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A216" s="1" t="s">
         <v>726</v>
       </c>
@@ -20633,7 +20633,7 @@
       <c r="G216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A217" s="1" t="s">
         <v>727</v>
       </c>
@@ -20655,7 +20655,7 @@
       <c r="G217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A218" s="1" t="s">
         <v>728</v>
       </c>
@@ -20677,7 +20677,7 @@
       <c r="G218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A219" s="1" t="s">
         <v>729</v>
       </c>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A220" s="1" t="s">
         <v>730</v>
       </c>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A221" s="1" t="s">
         <v>731</v>
       </c>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A222" s="1" t="s">
         <v>732</v>
       </c>
@@ -20776,7 +20776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A223" s="1" t="s">
         <v>733</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A224" s="1" t="s">
         <v>734</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A225" s="1" t="s">
         <v>735</v>
       </c>
@@ -20851,7 +20851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A226" s="1" t="s">
         <v>736</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A227" s="1" t="s">
         <v>737</v>
       </c>
@@ -20900,7 +20900,7 @@
       <c r="G227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>738</v>
       </c>
@@ -20926,7 +20926,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>739</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="230" spans="1:15">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>740</v>
       </c>
@@ -20969,7 +20969,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>741</v>
       </c>
@@ -20983,7 +20983,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>742</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>743</v>
       </c>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B6ABAA-734E-4AAF-9CA0-315C978FDE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="631" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表.csv" sheetId="56" r:id="rId1"/>

--- a/Table/Design/设计表.xlsx
+++ b/Table/Design/设计表.xlsx
@@ -14517,8 +14517,10 @@
       <c r="F9" t="s">
         <v>694</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>1147</v>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你发动的所有攻击伤害额外 +1 ；（攻击命中时②，若你的【手牌】数 &gt;3 ）本次攻击伤害额外 +1 。</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14540,8 +14542,10 @@
       <c r="F10" t="s">
         <v>694</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>1148</v>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（作为主动攻击打出时发动）\n ●（若命中后②对手的【手牌】为 2 ）本次攻击伤害额外 +2 ；\n ●（若命中后②对手的【手牌】为 3 ）本次攻击伤害额外 +1 ；</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14704,8 +14708,10 @@
       <c r="F17" t="s">
         <v>702</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>1155</v>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【水晶】目标角色【手牌】补到 5 张【强制】，额外 +1 【攻击行动】。</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -14871,9 +14877,6 @@
       <c r="H24" t="s">
         <v>1163</v>
       </c>
-      <c r="I24" t="s">
-        <v>1164</v>
-      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
@@ -14897,9 +14900,6 @@
       <c r="G25" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="H25" t="s">
-        <v>455</v>
-      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
@@ -14972,8 +14972,10 @@
       <c r="F28" t="s">
         <v>707</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>1169</v>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】你可选择摸 1 张牌，【横置】持续到你的下个行动阶段开始时，你的【手牌】上限 -1 ；你不能成为主动攻击的目标；你的主动攻击对手无法应战且伤害额外+X，X为你剩余的【能量】数。【潜行】的效果结束时【重置】。</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -14998,11 +15000,15 @@
       <c r="G29" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="H29" t="s">
-        <v>1171</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1172</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【冰霜祷言】：令目标 +1 【治疗】</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">点头像选择 1 名角色 +1 【治疗】，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -15027,11 +15033,10 @@
       <c r="G30" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="H30" t="s">
-        <v>1174</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1175</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">点头像选择 1 名角色 +2 【治疗】，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -15056,11 +15061,10 @@
       <c r="G31" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="H31" t="s">
-        <v>1177</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1178</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">点头像选择 1~ 3 名不同的角色各 +1 【治疗】（不可重复），选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -15082,8 +15086,10 @@
       <c r="F32" t="s">
         <v>707</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>1179</v>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】【横置】你的【手牌】上限恒定为 7 【强制】，你 +1 【水晶】。</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -15108,11 +15114,10 @@
       <c r="G33" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="H33" t="s">
-        <v>1181</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1182</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">点头像分配 3 点【治疗】（同一人可点多次；点第 4 次重新分配），选满后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -15137,9 +15142,6 @@
       <c r="G34" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="H34" t="s">
-        <v>1184</v>
-      </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
@@ -15163,11 +15165,10 @@
       <c r="G35" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="H35" t="s">
-        <v>1186</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1187</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】交给 {src}</t>
+        </is>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -15192,8 +15193,10 @@
       <c r="G36" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="H36" t="s">
-        <v>1189</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【天使羁绊】：令目标 +1 【治疗】</t>
+        </is>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -15218,9 +15221,6 @@
       <c r="G37" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="H37" t="s">
-        <v>1190</v>
-      </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
@@ -15267,14 +15267,20 @@
       <c r="F39" t="s">
         <v>702</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="H39" t="s">
-        <v>1192</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1193</v>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X【水晶】为我方抵御X点因法术伤害而造成的【士气】下降。</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【神之庇护】：本次将损失 {损失} 点【士气】，要不要消耗【星石】抵挡？</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【神之庇护】：本次抵挡 {抵挡} 点【士气】损失，请选择要消耗的【星石】组合</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -15302,9 +15308,6 @@
       <c r="H40" t="s">
         <v>1195</v>
       </c>
-      <c r="I40" t="s">
-        <v>1196</v>
-      </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
@@ -15351,9 +15354,6 @@
       <c r="G42" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="H42" t="s">
-        <v>456</v>
-      </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
@@ -15377,9 +15377,6 @@
       <c r="G43" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="H43" t="s">
-        <v>1198</v>
-      </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
@@ -15492,17 +15489,20 @@
       <c r="F48" t="s">
         <v>694</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="H48" t="s">
-        <v>1203</v>
-      </c>
-      <c r="I48" t="s">
-        <v>1204</v>
-      </c>
-      <c r="J48" t="s">
-        <v>1205</v>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(仅【暗影形态】下发动，弃 2 张法术牌【展示】)对目标角色造成 2 点法术伤害③；(若你额外移除我方【战绩区】 2 【星石】)【重置】脱离【暗影形态】，你 +1 【宝石】。</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【暗影流星】：要不要额外移除我方【战绩区】 2 【星石】？</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【暗影流星】：请选择要移除的我方【战绩区】 2 【星石】组合</t>
+        </is>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -15524,11 +15524,15 @@
       <c r="F49" t="s">
         <v>707</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H49" t="s">
-        <v>1207</v>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】(主动攻击前发动①)本次攻击对手无法应战；(若命中②)你将【手牌】补至上限【强制】，然后弃 2 张牌。</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【黄泉震颤】：补满【手牌】后请弃 2 张牌</t>
+        </is>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -15576,11 +15580,10 @@
       <c r="G51" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="H51" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1211</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先选好要弃的水系牌：所有人各 +1 【治疗】，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -15605,11 +15608,10 @@
       <c r="G52" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="H52" t="s">
-        <v>1213</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1214</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先选好要弃的法术牌，再点一名有【治疗】的角色：他 -1 【治疗】、你 +1 【治疗】，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -15686,8 +15688,10 @@
       <c r="H55" t="s">
         <v>1219</v>
       </c>
-      <c r="I55" t="s">
-        <v>1220</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移除 {n} 点【治疗】，本次伤害 +{n}</t>
+        </is>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -15712,11 +15716,10 @@
       <c r="G56" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="H56" t="s">
-        <v>1222</v>
-      </c>
-      <c r="I56" t="s">
-        <v>1223</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消耗 1 【宝石】，你 +2 【治疗】（无视上限、最高到 5），并额外 +1 攻击行动</t>
+        </is>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -15764,9 +15767,6 @@
       <c r="G58" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="H58" t="s">
-        <v>1226</v>
-      </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
@@ -15905,9 +15905,6 @@
       <c r="G64" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="H64" t="s">
-        <v>1233</v>
-      </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1" t="s">
@@ -16026,11 +16023,10 @@
       <c r="G69" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="H69" t="s">
-        <v>1240</v>
-      </c>
-      <c r="I69" t="s">
-        <v>1241</v>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【偷天换日】：转移对方 1 个【宝石】，或把我方【战绩区】的【水晶】全部转为【宝石】</t>
+        </is>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -16098,11 +16094,10 @@
       <c r="F72" t="s">
         <v>694</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H72" t="s">
-        <v>1245</v>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(弃 1 张地系牌【展示】)对其他所有角色各造成 1 点法术伤害③；(若因此造成【士气】下降)回合结束时，你 +1 【治疗】。</t>
+        </is>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -16127,11 +16122,10 @@
       <c r="G73" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="H73" t="s">
-        <v>1247</v>
-      </c>
-      <c r="I73" t="s">
-        <v>1248</v>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消耗 {n} 点【治疗】</t>
+        </is>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -16156,9 +16150,6 @@
       <c r="G74" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="H74" t="s">
-        <v>1250</v>
-      </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1" t="s">
@@ -16228,9 +16219,6 @@
       <c r="G77" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="H77" t="s">
-        <v>457</v>
-      </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1" t="s">
@@ -16274,8 +16262,10 @@
       <c r="F79" t="s">
         <v>707</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>1254</v>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】【横置】转为【审判形态】，你的【手牌】上限恒定为 5 【恒定】；每次在你的回合开始时，你 +1 【审判】。</t>
+        </is>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -16297,17 +16287,20 @@
       <c r="F80" t="s">
         <v>702</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="H80" t="s">
-        <v>1256</v>
-      </c>
-      <c r="I80" t="s">
-        <v>1257</v>
-      </c>
-      <c r="J80" t="s">
-        <v>1258</v>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【水晶】你 +1 【审判】，再选择以下一项发动：\n ●弃掉你的所有【手牌】。\n ●将你的【手牌】补到上限【强制】，我方【战绩区】 +1 【宝石】。</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弃光【手牌】</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">补满【手牌】，我方 +1 【宝石】</t>
+        </is>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -16355,9 +16348,6 @@
       <c r="G82" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="H82" t="s">
-        <v>1261</v>
-      </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
@@ -16381,11 +16371,10 @@
       <c r="G83" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="H83" t="s">
-        <v>1263</v>
-      </c>
-      <c r="I83" t="s">
-        <v>1264</v>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】交给 {dst}</t>
+        </is>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -16433,8 +16422,10 @@
       <c r="G85" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H85" t="s">
-        <v>1062</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【神圣契约】：点击目标头像分配【治疗】，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -16459,11 +16450,10 @@
       <c r="G86" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="H86" t="s">
-        <v>1268</v>
-      </c>
-      <c r="I86" t="s">
-        <v>1269</v>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先选好要弃的牌，再点头像选目标，选好后点「确定」：选队友（含自己）→ 你 +2 【治疗】、他 +1 【治疗】；选敌人 → 你 -1 【治疗】、他受 2 点法术伤害（【治疗】不足时点不了敌人）</t>
+        </is>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -16488,9 +16478,6 @@
       <c r="G87" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="H87" t="s">
-        <v>1271</v>
-      </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
@@ -16514,9 +16501,6 @@
       <c r="G88" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="H88" t="s">
-        <v>1273</v>
-      </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
@@ -16543,9 +16527,6 @@
       <c r="H89" t="s">
         <v>1275</v>
       </c>
-      <c r="I89" t="s">
-        <v>1276</v>
-      </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="1" t="s">
@@ -16569,9 +16550,6 @@
       <c r="G90" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="H90" t="s">
-        <v>1278</v>
-      </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
@@ -16693,9 +16671,6 @@
       <c r="G95" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="H95" t="s">
-        <v>1504</v>
-      </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="1" t="s">
@@ -16719,9 +16694,6 @@
       <c r="G96" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="H96" t="s">
-        <v>1505</v>
-      </c>
     </row>
     <row r="97" spans="1:10" s="6" customFormat="1">
       <c r="A97" s="5" t="s">
@@ -16745,9 +16717,6 @@
       <c r="G97" s="5" t="s">
         <v>1287</v>
       </c>
-      <c r="H97" t="s">
-        <v>1288</v>
-      </c>
     </row>
     <row r="98" spans="1:10" s="6" customFormat="1">
       <c r="A98" s="5" t="s">
@@ -16771,9 +16740,6 @@
       <c r="G98" s="5" t="s">
         <v>1289</v>
       </c>
-      <c r="H98" t="s">
-        <v>1290</v>
-      </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1" t="s">
@@ -16794,11 +16760,15 @@
       <c r="F99" t="s">
         <v>694</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="H99" t="s">
-        <v>1292</v>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你每次发动【灵符】，可将自己 1 张【手牌】面朝下放置在你的角色旁，作为【妖力】。</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【念咒】：把 {n} 张【手牌】作为【妖力】</t>
+        </is>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -16950,8 +16920,10 @@
       <c r="F105" t="s">
         <v>694</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>1303</v>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(主动攻击前发动①，移除 1 个【天使之魂】)本次攻击若命中②，你 +2 【治疗】；若未命中②，我方 +1 【士气】；不能和【剑魂守护】同时发动。</t>
+        </is>
       </c>
       <c r="H105" t="s">
         <v>1304</v>
@@ -17230,8 +17202,10 @@
       <c r="F117" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G117" s="13" t="s">
-        <v>1317</v>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（发动【禁断之力】后强制触发【强制】）【横置】额外 +1 【攻击行动】；持续到你的下个行动阶段开始，你的【手牌】上限恒定为 4 【恒定】。【精疲力竭】的效果结束时【重置】，并对自己造成 3 点法术伤害③。</t>
+        </is>
       </c>
     </row>
     <row r="118" spans="1:11" s="12" customFormat="1">
@@ -17279,9 +17253,6 @@
       <c r="G119" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="H119" t="s">
-        <v>1320</v>
-      </c>
     </row>
     <row r="120" spans="1:11" s="12" customFormat="1">
       <c r="A120" s="13" t="s">
@@ -17302,11 +17273,15 @@
       <c r="F120" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="G120" s="13" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H120" t="s">
-        <v>1322</v>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【水晶】（主动攻击命中或未命中时发动②）弃掉你所有【手牌】【展示】，其中每有 1 张法术牌，你 +1 【怒气】；（若未命中②）其中每有 1 张水系牌，你 +1 【知性】；（若命中②）其中每有 1 张火系牌，本次攻击伤害额外 +1 ，并对自己造成等同于火系牌数量的法术伤害③。</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【禁断之力】：弃掉全部 {n} 张【手牌】</t>
+        </is>
       </c>
     </row>
     <row r="121" spans="1:11" s="12" customFormat="1">
@@ -17328,8 +17303,10 @@
       <c r="F121" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="G121" s="13" t="s">
-        <v>1323</v>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】（承受法术伤害时发动⑥）你 +3 【怒气】；（若此伤害造成【士气】实际下降）本次下降的【士气】值恒定为 1 【恒定】。</t>
+        </is>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -17351,8 +17328,10 @@
       <c r="F122" t="s">
         <v>694</v>
       </c>
-      <c r="G122" s="1" t="s">
-        <v>1324</v>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(我方每有 1 点【士气】下降)你 +1 【黄色灵魂】。</t>
+        </is>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -17377,9 +17356,6 @@
       <c r="G123" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="H123" t="s">
-        <v>1325</v>
-      </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="1" t="s">
@@ -17432,8 +17408,10 @@
       <c r="F125" t="s">
         <v>694</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>1330</v>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(移除 2 点【黄色灵魂】)你弃 2 张牌，目标角色摸 2 张牌【强制】(但最多补到其【手牌】上限)。</t>
+        </is>
       </c>
       <c r="H125" t="s">
         <v>1331</v>
@@ -17458,11 +17436,10 @@
       <c r="F126" t="s">
         <v>694</v>
       </c>
-      <c r="G126" s="1" t="s">
-        <v>1332</v>
-      </c>
-      <c r="H126" t="s">
-        <v>1506</v>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(移除 3 点【黄色灵魂】)对目标角色造成 3 点法术伤害③，(若他【手牌】 &lt;3 且【手牌】上限 &gt;5 )则本次法术伤害额外 +2 。</t>
+        </is>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -17487,9 +17464,6 @@
       <c r="G127" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="H127" t="s">
-        <v>1334</v>
-      </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="1" t="s">
@@ -17510,6 +17484,11 @@
       <c r="F128" t="s">
         <v>694</v>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（仅你队友数 &gt;1 时可发动，移除 1 点【黄色灵魂】和 1 点【蓝色灵魂】）将此卡放置于目标队友面前。（若你拥有【灵魂链接】，每当你或灵魂术士将承受伤害前⑥，灵魂术士移除X点【蓝色灵魂】）将X点伤害转移给另一方，转移后的伤害为法术伤害⑥。</t>
+        </is>
+      </c>
       <c r="H128" t="s">
         <v>1336</v>
       </c>
@@ -17521,9 +17500,6 @@
       </c>
       <c r="K128" t="s">
         <v>1339</v>
-      </c>
-      <c r="G128" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -17597,8 +17573,10 @@
       <c r="F131" t="s">
         <v>694</v>
       </c>
-      <c r="G131" s="1" t="s">
-        <v>1344</v>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（当你在【普通形态】下因承受伤害而导致我方【士气】减少时强制发动【强制】）【横置】转为【流血形态】，你 +1 【治疗】，此形态下在你的每次回合开始时对自己造成 1 点法术伤害③。（自身【手牌】 &lt;3 时强制触发【强制】）【重置】脱离【流血形态】。</t>
+        </is>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -17623,9 +17601,6 @@
       <c r="G132" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="H132" t="s">
-        <v>1346</v>
-      </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="1" t="s">
@@ -17658,9 +17633,6 @@
       <c r="J133" t="s">
         <v>1350</v>
       </c>
-      <c r="K133" t="s">
-        <v>1351</v>
-      </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="1" t="s">
@@ -17681,11 +17653,10 @@
       <c r="F134" t="s">
         <v>694</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>1352</v>
-      </c>
-      <c r="H134" t="s">
-        <v>1353</v>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（摸 2 张牌【强制】，将【同生共死】放置于目标角色面前）\n在【普通形态】下，你和他【手牌】上限各 -2 。\n在【流血形态】下，你和他【手牌】上限各 +1 。</t>
+        </is>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -17710,9 +17681,6 @@
       <c r="G135" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="H135" t="s">
-        <v>1355</v>
-      </c>
     </row>
     <row r="136" spans="1:11" s="12" customFormat="1">
       <c r="A136" s="13" t="s">
@@ -17733,8 +17701,10 @@
       <c r="F136" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G136" s="13" t="s">
-        <v>1356</v>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你的【手牌】上限-X，X为你拥有的【蛹】的数量，但你的【手牌】上限最少为 3 【恒定】。</t>
+        </is>
       </c>
     </row>
     <row r="137" spans="1:11" s="12" customFormat="1">
@@ -17765,9 +17735,6 @@
       <c r="I137" t="s">
         <v>1359</v>
       </c>
-      <c r="J137" t="s">
-        <v>1360</v>
-      </c>
     </row>
     <row r="138" spans="1:11" s="12" customFormat="1">
       <c r="A138" s="13" t="s">
@@ -17791,8 +17758,10 @@
       <c r="G138" s="13" t="s">
         <v>1361</v>
       </c>
-      <c r="H138" t="s">
-        <v>1362</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【毒粉】：移除 {n} 个【茧】，该次伤害额外 +1</t>
+        </is>
       </c>
     </row>
     <row r="139" spans="1:11" s="12" customFormat="1">
@@ -17866,8 +17835,10 @@
       <c r="F141" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G141" s="13" t="s">
-        <v>1367</v>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（你每次移除【茧】时，若为法术牌，可展示之【展示】）你对目标角色造成 1 点法术伤害③，再对自己造成 2 点法术伤害③；此技能发动后，直到你的下个回合开始前，对方的【士气】最少为 1 【强制】。</t>
+        </is>
       </c>
       <c r="H141" t="s">
         <v>1368</v>
@@ -17895,9 +17866,6 @@
       <c r="G142" s="13" t="s">
         <v>1369</v>
       </c>
-      <c r="H142" t="s">
-        <v>1370</v>
-      </c>
     </row>
     <row r="143" spans="1:11" s="12" customFormat="1">
       <c r="A143" s="13" t="s">
@@ -17921,17 +17889,16 @@
       <c r="G143" s="13" t="s">
         <v>1371</v>
       </c>
-      <c r="H143" t="s">
-        <v>1372</v>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对目标角色造成 1 点法术伤害，不能用【治疗】抵挡</t>
+        </is>
       </c>
       <c r="I143" t="s">
         <v>1373</v>
       </c>
       <c r="J143" t="s">
         <v>1374</v>
-      </c>
-      <c r="K143" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -17979,9 +17946,6 @@
       <c r="G145" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="H145" t="s">
-        <v>1378</v>
-      </c>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="1" t="s">
@@ -18025,8 +17989,10 @@
       <c r="F147" t="s">
         <v>694</v>
       </c>
-      <c r="G147" s="1" t="s">
-        <v>1379</v>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（回合开始时，若你处于【英灵形态】）选择以下一项发动：\n ●你 +1 【治疗】，【重置】脱离【英灵形态】。\n ●（移除我方【战绩区】X个【星石】，X &lt;3 ）目标角色+X【治疗】。</t>
+        </is>
       </c>
       <c r="H147" t="s">
         <v>1380</v>
@@ -18034,8 +18000,10 @@
       <c r="I147" t="s">
         <v>1381</v>
       </c>
-      <c r="J147" t="s">
-        <v>1507</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移除我方【战绩区】X 个【星石】（X &lt;3），由你选择一个目标角色 +X【治疗】</t>
+        </is>
       </c>
       <c r="K147" t="s">
         <v>1382</v>
@@ -18092,8 +18060,10 @@
       <c r="F149" t="s">
         <v>694</v>
       </c>
-      <c r="G149" s="1" t="s">
-        <v>1387</v>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(主动攻击前发动①，移除 1 个火系【充能】)本次攻击伤害额外 +1 ，不能攻击【手牌】达到上限的对手；(若命中②，额外移除 1 个火系【充能】)本次攻击伤害额外 +1 ；(若未命中②)对对手造成 3 点法术伤害③；本回合你不能发动【多重射击】。</t>
+        </is>
       </c>
       <c r="H149" t="s">
         <v>1388</v>
@@ -18124,11 +18094,10 @@
       <c r="G150" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="H150" t="s">
-        <v>1391</v>
-      </c>
-      <c r="I150" t="s">
-        <v>1392</v>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【雷光散射】：选择更多雷系【充能】可对选定目标额外造成伤害，选好后点「确定」</t>
+        </is>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -18176,11 +18145,15 @@
       <c r="F152" t="s">
         <v>702</v>
       </c>
-      <c r="G152" s="1" t="s">
-        <v>1395</v>
-      </c>
-      <c r="H152" t="s">
-        <v>1396</v>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【水晶】你弃到 4 张牌，摸X张牌【强制】，可将自己最多X张【手牌】面朝下放置在你的角色旁，作为【充能】(X &lt;5 )；本回合你不能发动【魔贯冲击】和【雷光散射】。</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【充能】：把至多 {n} 张【手牌】作为【充能】</t>
+        </is>
       </c>
       <c r="I152" t="s">
         <v>1397</v>
@@ -18205,11 +18178,15 @@
       <c r="F153" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="G153" s="1" t="s">
-        <v>1398</v>
-      </c>
-      <c r="H153" t="s">
-        <v>1399</v>
+      <c r="G153" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】目标角色弃 1 张牌或你摸 3 张牌【强制】，将自己 1 张【手牌】面朝下放置在你的角色旁，作为【充能】，你 +1 【水晶】。</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【魔眼】：把 {n} 张【手牌】作为【充能】</t>
+        </is>
       </c>
       <c r="I153" t="s">
         <v>1400</v>
@@ -18321,11 +18298,15 @@
       <c r="G157" s="9" t="s">
         <v>1409</v>
       </c>
-      <c r="H157" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I157" t="s">
-        <v>1410</v>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">魔纹融合</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">魔纹融合（额外翻转 {n} 个【魔纹】，伤害 +{n}）</t>
+        </is>
       </c>
     </row>
     <row r="158" spans="1:13" s="8" customFormat="1">
@@ -18347,8 +18328,10 @@
       <c r="F158" s="8" t="s">
         <v>707</v>
       </c>
-      <c r="G158" s="7" t="s">
-        <v>1411</v>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】【横置】持续到你的回合结束时，你都处于【蓄势迸发形态】，此形态下你的【手牌】上限 +1 ；摸 1 张牌【强制】并任意调整你的【战纹】和【魔纹】；脱离【蓄势迸发形态】时【重置】。</t>
+        </is>
       </c>
       <c r="H158" t="s">
         <v>1412</v>
@@ -18373,8 +18356,10 @@
       <c r="F159" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="G159" s="7" t="s">
-        <v>1413</v>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【水晶】（对目标角色造成攻击或法术伤害时发动③）对另一目标角色造成X点法术伤害③，X与本次伤害相同但最高为 3 。【双重回响】的伤害不会造成【士气】下降。</t>
+        </is>
       </c>
       <c r="H159" t="s">
         <v>1414</v>
@@ -18494,8 +18479,10 @@
       <c r="F164" t="s">
         <v>694</v>
       </c>
-      <c r="G164" s="1" t="s">
-        <v>1420</v>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（当你因承受伤害而导致我方【士气】下降时强制发动【强制】）【横置】转为【热血沸腾形态】，此形态下你承受伤害不会导致我方【士气】下降【强制】。在你的回合结束阶段，若你处于此形态，【重置】并脱离此形态【强制】，你 +2 【治疗】。</t>
+        </is>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -18543,9 +18530,6 @@
       <c r="G166" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="H166" t="s">
-        <v>1423</v>
-      </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="1" t="s">
@@ -18566,8 +18550,10 @@
       <c r="F167" t="s">
         <v>694</v>
       </c>
-      <c r="G167" s="1" t="s">
-        <v>1424</v>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【横置】转为【幻影形态】，你的【手牌】上限恒定为 5 【恒定】；本回合你的下次主动攻击伤害额外 +1 ，但不能发动【漆黑之枪】和【充盈】。</t>
+        </is>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -18589,8 +18575,10 @@
       <c r="F168" t="s">
         <v>694</v>
       </c>
-      <c r="G168" s="1" t="s">
-        <v>1425</v>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（仅【幻影形态】下发动，对自己造成 2 点法术伤害③）【重置】脱离【幻影形态】；若没有因此造成我方【士气】下降，则对目标角色造成 2 点法术伤害③。</t>
+        </is>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -18638,8 +18626,10 @@
       <c r="G170" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="H170" t="s">
-        <v>1063</v>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【暗之障壁】：受到 {伤害} 伤害，弃任意数量的法术牌或雷系牌</t>
+        </is>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -18664,11 +18654,10 @@
       <c r="G171" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="H171" t="s">
-        <v>1427</v>
-      </c>
-      <c r="I171" t="s">
-        <v>1428</v>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -18690,14 +18679,20 @@
       <c r="F172" t="s">
         <v>702</v>
       </c>
-      <c r="G172" s="1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="H172" t="s">
-        <v>1430</v>
-      </c>
-      <c r="I172" t="s">
-        <v>1431</v>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X【水晶】（仅【幻影形态】下，主动攻击【手牌】为 1 或 2 的对手并命中后发动②）本次攻击伤害额外+(X +2 )。</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">投入 {n} 点【能量】（伤害 +{n2}）</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【漆黑之枪】：选择投入的【能量】</t>
+        </is>
       </c>
     </row>
     <row r="173" spans="1:10" s="12" customFormat="1">
@@ -18722,9 +18717,6 @@
       <c r="G173" s="15" t="s">
         <v>1432</v>
       </c>
-      <c r="H173" t="s">
-        <v>1433</v>
-      </c>
     </row>
     <row r="174" spans="1:10" s="12" customFormat="1">
       <c r="A174" s="15" t="s">
@@ -18745,11 +18737,10 @@
       <c r="F174" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G174" s="15" t="s">
-        <v>1434</v>
-      </c>
-      <c r="H174" t="s">
-        <v>1435</v>
+      <c r="G174" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（弃 2 张火系牌【展示】，移除 1 点【重生】）对目标角色和自己各造成 3 点法术伤害③，（若我方【士气】落后于该目标）本次法术伤害额外 +1 【强制】。</t>
+        </is>
       </c>
     </row>
     <row r="175" spans="1:10" s="12" customFormat="1">
@@ -18771,8 +18762,10 @@
       <c r="F175" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G175" s="15" t="s">
-        <v>1436</v>
+      <c r="G175" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（【手牌】 &lt;4 张时）【横置】摸 0 -2 张牌，数值由你决定，持续到你的下个行动阶段开始前，你都处于【烈焰形态】，在此形态下你的所有除水系和暗系外的攻击牌均视为火系【强制】，你发动【天火断空】时无需移除【重生】，你的【手牌】上限+(X -2 )（X为你的【重生】数量）；脱离【烈焰形态】时【重置】。</t>
+        </is>
       </c>
       <c r="H175" t="s">
         <v>1437</v>
@@ -18829,8 +18822,10 @@
       <c r="F177" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="G177" s="15" t="s">
-        <v>1441</v>
+      <c r="G177" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（当你因承受法术伤害而造成【士气】下降时）你 +1 【重生】。</t>
+        </is>
       </c>
     </row>
     <row r="178" spans="1:12" s="12" customFormat="1">
@@ -18855,9 +18850,6 @@
       <c r="G178" s="15" t="s">
         <v>1442</v>
       </c>
-      <c r="H178" t="s">
-        <v>1443</v>
-      </c>
     </row>
     <row r="179" spans="1:12" s="12" customFormat="1">
       <c r="A179" s="15" t="s">
@@ -18881,8 +18873,10 @@
       <c r="G179" s="15" t="s">
         <v>1444</v>
       </c>
-      <c r="H179" t="s">
-        <v>1445</v>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【魔能反转】：弃大于 2 张法术牌，造成弃置数量 -1 法术伤害</t>
+        </is>
       </c>
     </row>
     <row r="180" spans="1:12" s="8" customFormat="1">
@@ -18933,11 +18927,15 @@
       <c r="G181" s="14" t="s">
         <v>1448</v>
       </c>
-      <c r="H181" t="s">
-        <v>1427</v>
-      </c>
-      <c r="I181" t="s">
-        <v>1449</v>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移除 {n} 点【灵感】，双方各摸 {n2} 张牌</t>
+        </is>
       </c>
     </row>
     <row r="182" spans="1:12" s="8" customFormat="1">
@@ -19011,14 +19009,18 @@
       <c r="F184" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="G184" s="14" t="s">
-        <v>1454</v>
+      <c r="G184" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">（回合结束时若你拥有【永恒乐章】）选择以下一项执行：\n ●将我方【战绩区】的 1 【星石】提炼成为你的【能量】。\n ●为我方【战绩区】 +1 【宝石】，你 +1 【治疗】。</t>
+        </is>
       </c>
       <c r="H184" t="s">
         <v>1455</v>
       </c>
-      <c r="I184" t="s">
-        <v>1456</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将己方【战绩区】的 1 【星石】提炼为你的【能量】</t>
+        </is>
       </c>
       <c r="J184" t="s">
         <v>1457</v>
@@ -19104,8 +19106,10 @@
       <c r="G187" s="15" t="s">
         <v>1486</v>
       </c>
-      <c r="H187" t="s">
-        <v>1489</v>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弃 {n} 张【手牌】【强制】</t>
+        </is>
       </c>
       <c r="I187" t="s">
         <v>1503</v>
@@ -19130,8 +19134,10 @@
       <c r="F188" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="G188" s="15" t="s">
-        <v>1487</v>
+      <c r="G188" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【宝石】【横置】转为【精灵祝福形态】，将牌库顶的 3 张牌面朝下放置于角色旁作为【祝福】。此形态下你的【祝福】可视为【手牌】使用或打出。(你的回合结束时，若你未拥有【祝福】)【重置】脱离【精灵祝福形态】，对目标角色造成 2 点法术伤害③。</t>
+        </is>
       </c>
       <c r="H188" t="s">
         <v>1462</v>
@@ -19159,9 +19165,6 @@
       <c r="G189" s="15" t="s">
         <v>1488</v>
       </c>
-      <c r="H189" t="s">
-        <v>1490</v>
-      </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="1" t="s">
@@ -19450,8 +19453,10 @@
         <v>694</v>
       </c>
       <c r="G202" s="1"/>
-      <c r="H202" t="s">
-        <v>1468</v>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【美杜莎之眼】：移除 {n} 张【盖牌】并选目标</t>
+        </is>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -19474,8 +19479,10 @@
         <v>694</v>
       </c>
       <c r="G203" s="1"/>
-      <c r="H203" t="s">
-        <v>1469</v>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【月之轮回】：弃 {n} 张【盖牌】并选目标</t>
+        </is>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -19498,8 +19505,10 @@
         <v>694</v>
       </c>
       <c r="G204" s="1"/>
-      <c r="H204" t="s">
-        <v>1470</v>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【月渎】：耗 1 点【治疗】对目标造成 1 点伤害</t>
+        </is>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -19630,8 +19639,10 @@
         <v>694</v>
       </c>
       <c r="G210" s="1"/>
-      <c r="H210" t="s">
-        <v>1427</v>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
       </c>
       <c r="I210" t="s">
         <v>1472</v>
@@ -19657,8 +19668,10 @@
         <v>694</v>
       </c>
       <c r="G211" s="1"/>
-      <c r="H211" t="s">
-        <v>1427</v>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -19831,8 +19844,10 @@
         <v>919</v>
       </c>
       <c r="G219" s="1"/>
-      <c r="H219" t="s">
-        <v>1427</v>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -19855,8 +19870,10 @@
         <v>707</v>
       </c>
       <c r="G220" s="1"/>
-      <c r="H220" t="s">
-        <v>1475</v>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【自动填充】：选择转化的【能量】</t>
+        </is>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -19920,8 +19937,10 @@
       <c r="F223" t="s">
         <v>694</v>
       </c>
-      <c r="H223" t="s">
-        <v>1494</v>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">选择 1 名目标：该角色 +1 【治疗】</t>
+        </is>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -20074,8 +20093,10 @@
       <c r="F230" t="s">
         <v>915</v>
       </c>
-      <c r="H230" t="s">
-        <v>1427</v>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请选择 {n} 张【手牌】弃掉</t>
+        </is>
       </c>
       <c r="I230" t="s">
         <v>1474</v>
@@ -20100,8 +20121,10 @@
       <c r="F231" t="s">
         <v>915</v>
       </c>
-      <c r="H231" t="s">
-        <v>1476</v>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发动【圣流星弹】：令目标 +1 【治疗】</t>
+        </is>
       </c>
     </row>
     <row r="232" spans="1:9">
